--- a/docs/xlsx/jobs-2026-10-21.xlsx
+++ b/docs/xlsx/jobs-2026-10-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="654">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1951 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>0404 Biological Science Technician</t>
+  </si>
+  <si>
+    <t>USDA-ARS</t>
+  </si>
+  <si>
+    <t>Pullman, WA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$40,736 - $65,599 per year</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-0404-biological-science-technician-pullman-washington/9800669918</t>
+  </si>
+  <si>
+    <t>AmeriCorps Crew Leader</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Conservancy</t>
+  </si>
+  <si>
+    <t>Estes Park, CO</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-crew-leader-estes-park-colorado/4189607019</t>
+  </si>
+  <si>
+    <t>Animal Care Manager / Lead Keeper (Multiple Openings)</t>
+  </si>
+  <si>
+    <t>Family Fun Group</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>$25 - $35 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-manager--lead-keeper-multiple-openings-houston-texas/5084196101</t>
+  </si>
+  <si>
+    <t>Assistant Hatchery Manager - Trail Lakes Hatchery</t>
+  </si>
+  <si>
+    <t>Cook Inlet Aquaculture Association</t>
+  </si>
+  <si>
+    <t>Moose Pass, AK</t>
+  </si>
+  <si>
+    <t>$53,646 - $70,065 per year</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-hatchery-manager---trail-lakes-hatchery-moose-pass-alaska/3062089550</t>
+  </si>
+  <si>
+    <t>Bookkeeper/Associate Director of Finance</t>
+  </si>
+  <si>
+    <t>Teatown Lake Reservation</t>
+  </si>
+  <si>
+    <t>Ossining, NY</t>
+  </si>
+  <si>
+    <t>$70,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bookkeeperassociate-director-of-finance-ossining-new-york/5628920890</t>
+  </si>
+  <si>
+    <t>Botany Crew Member - SCA</t>
+  </si>
+  <si>
+    <t>U.S. Army Corps of Engineers - Willamette Valley Project</t>
+  </si>
+  <si>
+    <t>Junction City, OR</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$960 per week</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-botany-crew-member---sca-junction-city-oregon/4561394239</t>
+  </si>
+  <si>
+    <t>Certified Conservation Planner</t>
+  </si>
+  <si>
+    <t>DelAtlantic Conservation District</t>
+  </si>
+  <si>
+    <t>Mays Landing, NJ</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-certified-conservation-planner-mays-landing-new-jersey/4516340193</t>
+  </si>
+  <si>
+    <t>Civil Engineering Technician</t>
+  </si>
+  <si>
+    <t>Woodstown, NJ</t>
+  </si>
+  <si>
+    <t>$52,500 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-civil-engineering-technician-woodstown-new-jersey/8493431265</t>
+  </si>
+  <si>
+    <t>Climate Smart Agriculture Technical Assistance Coordinator</t>
+  </si>
+  <si>
+    <t>University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Bakersfield, CA</t>
+  </si>
+  <si>
+    <t>$69,825 - $97,020 per year</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>NAFSN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-climate-smart-agriculture-technical-assistance-coordinator-bakersfield-california/2506852163</t>
+  </si>
+  <si>
+    <t>Compliance Specialist</t>
+  </si>
+  <si>
+    <t>NEW Solutions</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$40 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-compliance-specialist-remote-remote/6929647901</t>
+  </si>
+  <si>
+    <t>Deputy Director (Deputy/Chief 6)</t>
+  </si>
+  <si>
+    <t>Oregon Department of Environmental Quality</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$11,429 - $17,704 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-deputychief-6-portland-oregon/4606947667</t>
+  </si>
+  <si>
+    <t>Deputy Director for Zero-Emission Vehicle Strategy, Planning, and Market Development</t>
+  </si>
+  <si>
+    <t>California Energy Commission</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$10,349 - $17,769 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-for-zero-emission-vehicle-strategy-planning-and-market-development-sacramento-ca-usa-california/8566576180</t>
+  </si>
+  <si>
+    <t>Director of Conservation Programs</t>
+  </si>
+  <si>
+    <t>Osa Conservation Costa Rica</t>
+  </si>
+  <si>
+    <t>Puntarenas, Latin America</t>
+  </si>
+  <si>
+    <t>Compensation will be determined based on experience; we highly value our team members.</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-conservation-programs-puntarenas-latin-america/3163613726</t>
+  </si>
+  <si>
+    <t>District Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Mesa Conservation District</t>
+  </si>
+  <si>
+    <t>Grand Junction, CO</t>
+  </si>
+  <si>
+    <t>$36 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-programs-coordinator-grand-junction-colorado/7629499241</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>Old Santee Canal Park</t>
+  </si>
+  <si>
+    <t>Moncks Corner, SC</t>
+  </si>
+  <si>
+    <t>$54,470 - $68,070 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-coordinator-moncks-corner-south-carolina/2664936295</t>
+  </si>
+  <si>
+    <t>Environmental Education Fellow</t>
+  </si>
+  <si>
+    <t>$450 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-fellow-estes-park-colorado/1545592733</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Grizzly &amp; Wolf Discovery Center</t>
+  </si>
+  <si>
+    <t>West Yellowstone, MT</t>
+  </si>
+  <si>
+    <t>$135,000 - $175,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-west-yellowstone-montana/8880331206</t>
+  </si>
+  <si>
+    <t>Facilities and Security Associate</t>
+  </si>
+  <si>
+    <t>San Diego Natural History Museum</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-facilities-and-security-associate-san-diego-california/5657665393</t>
+  </si>
+  <si>
+    <t>Field Organizer</t>
+  </si>
+  <si>
+    <t>Sierra Watch</t>
+  </si>
+  <si>
+    <t>Truckee, CA</t>
+  </si>
+  <si>
+    <t>$28 - $33 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-organizer-truckee-california/6006382743</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 1- American River RST Crew Lead</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>$21.71 - $34.96 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-1--american-river-rst-crew-lead-sacramento-california/6555276245</t>
+  </si>
+  <si>
+    <t>Forest Practices Rule &amp; Board Coordinator</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$59,760 - $80,496 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-practices-rule--board-coordinator-olympia-washington/5837125925</t>
+  </si>
+  <si>
+    <t>Laborer</t>
+  </si>
+  <si>
+    <t>Devils Postpile National Monument</t>
+  </si>
+  <si>
+    <t>Mammoth Lakes, CA</t>
+  </si>
+  <si>
+    <t>$19.46 - $32.61 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-laborer-mammoth-lakes-california/1323851762</t>
+  </si>
+  <si>
+    <t>Maintenance Mechanic (Facilities)</t>
+  </si>
+  <si>
+    <t>$20.31 - $33.68 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-mechanic-facilities-mammoth-lakes-california/1931175180</t>
+  </si>
+  <si>
+    <t>Maintenance Supervisor</t>
+  </si>
+  <si>
+    <t>Vermejo, Ted Turner Reserve</t>
+  </si>
+  <si>
+    <t>Raton, NM</t>
+  </si>
+  <si>
+    <t>Commensurate with Experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-supervisor-raton-new-mexico/7605186568</t>
+  </si>
+  <si>
+    <t>Maintenance Worker (Trails)</t>
+  </si>
+  <si>
+    <t>$21.18 - $39 per hour</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-worker-mammoth-lakes-california/9787538364</t>
+  </si>
+  <si>
+    <t>Naturalist Sea Kayak Guide</t>
+  </si>
+  <si>
+    <t>Sea Quest Kayak Tours</t>
+  </si>
+  <si>
+    <t>Friday Harbor, WA</t>
+  </si>
+  <si>
+    <t>$115 - $300 per day</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-naturalist-sea-kayak-guide-friday-harbor-washington/8966042021</t>
+  </si>
+  <si>
+    <t>Outdoor Education Fellow</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-education-fellow-estes-park-colorado/4772385906</t>
+  </si>
+  <si>
+    <t>Park Ranger (General)</t>
+  </si>
+  <si>
+    <t>$19.52 - $31.43 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-park-ranger-general-mammoth-lakes-california/2862814885</t>
+  </si>
+  <si>
+    <t>Park Ranger (Interpretation)</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-park-ranger-interpretation-mammoth-lakes-california/3219148074</t>
+  </si>
+  <si>
+    <t>Plant Conservation Specialist I</t>
+  </si>
+  <si>
+    <t>Mojave Desert Land Trust</t>
+  </si>
+  <si>
+    <t>Joshua Tree, CA</t>
+  </si>
+  <si>
+    <t>$22.50 - $23.50 per hour</t>
+  </si>
+  <si>
+    <t>botany-land-trust-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-plant-conservation-specialist-i-joshua-tree-california/9241764157</t>
+  </si>
+  <si>
+    <t>Research Assistant (Water Department)</t>
+  </si>
+  <si>
+    <t>County of Inyo (CA)</t>
+  </si>
+  <si>
+    <t>Independence, CA</t>
+  </si>
+  <si>
+    <t>$65,701.68 - $85,364.28 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-assistant-water-department-independence-california/5291068346</t>
+  </si>
+  <si>
+    <t>Technical Services Manager</t>
+  </si>
+  <si>
+    <t>Sequoia Ecological Consulting</t>
+  </si>
+  <si>
+    <t>Remote, CA</t>
+  </si>
+  <si>
+    <t>$140,000 - $160,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-technical-services-manager-remote-california/7746166476</t>
+  </si>
+  <si>
+    <t>TerraCorps AmeriCorps Service Member</t>
+  </si>
+  <si>
+    <t>TerraCorps</t>
+  </si>
+  <si>
+    <t>Providence, RI</t>
+  </si>
+  <si>
+    <t>$19,656 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-terracorps-americorps-service-member-providence-rhode-island/2992333663</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-terracorps-americorps-service-member-boston-massachusetts/1597266205</t>
+  </si>
+  <si>
+    <t>TPWD - Maintenance Specialist I (Operations Ranger-Fluctuating Hours)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>El Paso, TX</t>
+  </si>
+  <si>
+    <t>$20.34 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---maintenance-specialist-i-operations-ranger-fluctuating-hours-el-paso-texas/2818247995</t>
+  </si>
+  <si>
+    <t>TPWD - Maintenance Specialist III (Operations Ranger)</t>
+  </si>
+  <si>
+    <t>Colorado City, TX</t>
+  </si>
+  <si>
+    <t>$3,920.64 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---maintenance-specialist-iii-operations-ranger-colorado-city-texas/7527395283</t>
+  </si>
+  <si>
+    <t>Wildlife Specialist</t>
+  </si>
+  <si>
+    <t>USDA APHIS Wildlife Services</t>
+  </si>
+  <si>
+    <t>Various, IA</t>
+  </si>
+  <si>
+    <t>$37,193 - $59,621 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-specialist-various-iowa/3251059414</t>
+  </si>
+  <si>
+    <t>Writer and Communications Specialist</t>
+  </si>
+  <si>
+    <t>Southern Utah Wilderness Alliance</t>
+  </si>
+  <si>
+    <t>Salt Lake City, UT</t>
+  </si>
+  <si>
+    <t>$57,000 - $62,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-writer-and-communications-specialist-salt-lake-city-utah/8125806562</t>
+  </si>
+  <si>
+    <t>Social Media Intern</t>
+  </si>
+  <si>
+    <t>Commission Shift</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>Less than 20,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/social-media-intern/</t>
+  </si>
+  <si>
+    <t>Administrative Assistant (Bilingual English/Spanish)</t>
+  </si>
+  <si>
+    <t>Life Span</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Victim Support, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef9f369b39b14708a1f5d862d2cc4cc5-administrative-assistant-bilingual-englishspanish-life-span-chicago</t>
+  </si>
+  <si>
+    <t>Advisor, Salesforce Solutions</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>USD 87360.00 - 120640.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e8e6bfccad584ca5ba2261bd615fbd33-advisor-salesforce-solutions-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Business and Cooperative Development Specialist</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Urban Areas, Immigrants Or Refugees, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0b8451ecdc547228080debab3028427-business-and-cooperative-development-specialist-masa-bronx</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Center for Early Learning Excellence</t>
+  </si>
+  <si>
+    <t>Baton Rouge, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c59fc3ca8314fe19d8d6acc1a7b4dc1-chief-executive-officer-center-for-early-learning-excellence-baton-rouge</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>The Oakland Zoo</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 189223.00 - 210247.78/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b679873612394efeb522d0c745c0a111-chief-financial-officer-the-oakland-zoo-oakland</t>
+  </si>
+  <si>
+    <t>Child Abuse Prevention Training Specialist</t>
+  </si>
+  <si>
+    <t>Healing New York</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27696f74a8ff4c0e833443a6a4813fe2-child-abuse-prevention-training-specialist-healing-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>United Jewish Council of the East Side, Inc.</t>
+  </si>
+  <si>
+    <t>USD 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1d88acf4d15438688c94c142a434431-controller-united-jewish-council-of-the-east-side-inc-new-york</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>The Salvation Army</t>
+  </si>
+  <si>
+    <t>Fayetteville, Arkansas</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0742c393362a4f799d9c3e92a162e579-development-director-the-salvation-army-fayetteville</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT MANAGER</t>
+  </si>
+  <si>
+    <t>American Business Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/489915a106f04c20abc82995292ba509-development-manager-american-business-immigration-coalition-chicago</t>
+  </si>
+  <si>
+    <t>Development Officer, Special Events</t>
+  </si>
+  <si>
+    <t>SEEDS - Access Changes Everything</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c449635aba0e46f3a1b8348bd18cbb30-development-officer-special-events-seeds-access-changes-everything-newark</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Friends of the Dallas Public Library</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a8ff3878c744e0b84844f7bc893d5c7-director-of-development-friends-of-the-dallas-public-library-dallas</t>
+  </si>
+  <si>
+    <t>National Council For Adoption</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecb96549bf6240e0ac0c03a971e20132-director-of-development-national-council-for-adoption-alexandria</t>
+  </si>
+  <si>
+    <t>Director of Workforce Development at Immigrant Family Services Institute</t>
+  </si>
+  <si>
+    <t>Immigrant Family Services Institute</t>
+  </si>
+  <si>
+    <t>Mattapan, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/413a6946eff948828d7d2cb0d83d317d-director-of-workforce-development-at-immigrant-family-services-institute-immigrant-family-services-institute-mattapan</t>
+  </si>
+  <si>
+    <t>Director Programs Afghanistan</t>
+  </si>
+  <si>
+    <t>Welthungerhilfe</t>
+  </si>
+  <si>
+    <t>Kabul, Kabul, AF</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Agriculture, Disaster Relief, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/595f69d9d9834ff89e329cd87159f813-director-programs-afghanistan-welthungerhilfe-kabul</t>
+  </si>
+  <si>
+    <t>Director, Digital Strategy, Communications</t>
+  </si>
+  <si>
+    <t>Vera Institute of Justice</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Immigrants Or Refugees, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ef8cdec9f9b47b39f3714e19d5d857f-director-digital-strategy-communications-vera-institute-of-justice-new-york</t>
+  </si>
+  <si>
+    <t>Director, SAGE Center Harlem</t>
+  </si>
+  <si>
+    <t>SAGE | Advocacy and Services for LGBT Elders, Inc.</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e391e3e8c47643ecbe97d57d5458e657-director-sage-center-harlem-sage-advocacy-and-services-for-lgbt-elders-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director, Tax Policy</t>
+  </si>
+  <si>
+    <t>The Bipartisan Policy Center</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7500654856db481f9639ff441db9143d-director-tax-policy-the-bipartisan-policy-center-washington</t>
+  </si>
+  <si>
+    <t>Employment Coordinator</t>
+  </si>
+  <si>
+    <t>Japanese Community Youth Council</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1169b79b6c4e462aabaf456edbf903ef-employment-coordinator-japanese-community-youth-council-san-francisco</t>
+  </si>
+  <si>
+    <t>Executive Assistant, Development and Events</t>
+  </si>
+  <si>
+    <t>Catholic Charities Archdiocese of NY</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac398e14e15a4e8a9d94c6fd55fb7c6b-executive-assistant-development-and-events-catholic-charities-archdiocese-of-ny-new-york</t>
+  </si>
+  <si>
+    <t>Climate and Health Funders Coalition</t>
+  </si>
+  <si>
+    <t>London, England, GB</t>
+  </si>
+  <si>
+    <t>GBP 170000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3a98fc9cb9ed4cf085ecc66ab77f8f55-executive-director-climate-and-health-funders-coalition-london</t>
+  </si>
+  <si>
+    <t>Association of Infant Mental Health in Tennessee</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Environment, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/71190f46e933477896fce5548ff8b951-executive-director-association-of-infant-mental-health-in-tennessee-nashville</t>
+  </si>
+  <si>
+    <t>Executive Director, Mattapan Food and Fitness Coalition</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4286b89a1e364ac3867373e43b12ba8c-executive-director-mattapan-food-and-fitness-coalition-tsne-mattapan</t>
+  </si>
+  <si>
+    <t>Field Representative-Central California</t>
+  </si>
+  <si>
+    <t>California Federation of Teachers</t>
+  </si>
+  <si>
+    <t>Fresno, California</t>
+  </si>
+  <si>
+    <t>USD 102802.00 - 143653.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/916ca008d93e47adbe17f6ba4ab9db4e-field-representative-central-california-california-federation-of-teachers-fresno</t>
+  </si>
+  <si>
+    <t>GCCFI Senior Program Manager</t>
+  </si>
+  <si>
+    <t>Grand Canyon Conservancy</t>
+  </si>
+  <si>
+    <t>Grand Canyon, Arizona</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/41810ecbcf3b41bf8b53701237e6eb2f-gccfi-senior-program-manager-grand-canyon-conservancy-grand-canyon</t>
+  </si>
+  <si>
+    <t>Human Resources Operations Manager</t>
+  </si>
+  <si>
+    <t>Harlem Grown</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef703179d32747f0836325005129fb44-human-resources-operations-manager-harlem-grown-new-york</t>
+  </si>
+  <si>
+    <t>Individual Giving Manager</t>
+  </si>
+  <si>
+    <t>Planned Parenthood Columbia Willamette</t>
+  </si>
+  <si>
+    <t>USD 75004.00 - 109304.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a8dd7c5eb1e4b9a99c2b6a9b3a36004-individual-giving-manager-planned-parenthood-columbia-willamette-portland</t>
+  </si>
+  <si>
+    <t>Language Justice Program Coordinator</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Urban Areas, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b4abc62ae4f48d3a5fd9702ab3fc4fb-language-justice-program-coordinator-masa-bronx</t>
+  </si>
+  <si>
+    <t>Lead I, Operations &amp; Strategy</t>
+  </si>
+  <si>
+    <t>The Education Trust -- Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 86070.00 - 107580.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0355665e43064372a0383740528d1422-lead-i-operations-strategy-the-education-trust-washington-dc-washington</t>
+  </si>
+  <si>
+    <t>Leadership Development Facilitator</t>
+  </si>
+  <si>
+    <t>The Termeer Institute</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Health Medicine, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fda0d9f6c40d46cc9b1f178ae4f547f1-leadership-development-facilitator-the-termeer-institute-cambridge</t>
+  </si>
+  <si>
+    <t>Lower School Assistant Teacher (Maternity Leave)</t>
+  </si>
+  <si>
+    <t>Brookwood School</t>
+  </si>
+  <si>
+    <t>Manchester-by-the-Sea, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/838b201c88d145919b7affaf8f9bab8c-lower-school-assistant-teacher-maternity-leave-brookwood-school-manchester-by-the-sea</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Riverdale Park, Maryland</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8d93ed360314d0da5a8769f40ffb8b2-major-gifts-officer-central-union-mission-riverdale-park</t>
+  </si>
+  <si>
+    <t>Manager of Finance and Accounting</t>
+  </si>
+  <si>
+    <t>The Denver Foundation</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 96750.00 - 112500.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/431fc40128294bf883dbb9ca8e31364e-manager-of-finance-and-accounting-the-denver-foundation-denver</t>
+  </si>
+  <si>
+    <t>Manager, Information Technology</t>
+  </si>
+  <si>
+    <t>William T. Grant Foundation</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30ae919c9aea446586bfb399bc335f2a-manager-information-technology-william-t-grant-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Manager/Senior Manager of Policy</t>
+  </si>
+  <si>
+    <t>Healthier Colorado</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8ab0232a2cc4fe39f12bde7821e4f5d-managersenior-manager-of-policy-healthier-colorado-denver</t>
+  </si>
+  <si>
+    <t>Managing Director, Baybrook Revitalization Fund</t>
+  </si>
+  <si>
+    <t>Greater Baybrook Alliance</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5a2f9899ba6497fb5b54fc0205077ee-managing-director-baybrook-revitalization-fund-greater-baybrook-alliance-baltimore</t>
+  </si>
+  <si>
+    <t>Operations and Data Coordinator</t>
+  </si>
+  <si>
+    <t>Bethesda Cares, Inc.</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0b0788f5c87427dbec00449e925b528-operations-and-data-coordinator-bethesda-cares-inc-bethesda</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Center DC</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/074964ae96e24887bc8ae27bc7214bcc-operations-manager-center-dc-washington</t>
+  </si>
+  <si>
+    <t>Program Director - Posse Los Angeles</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09ad26a5820f4abf9009f3875d63f56e-program-director-posse-los-angeles-the-posse-foundation-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Program+Marketing Coordinator</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/340bc0c3ee554af094cfccbdd0305cc3-programmarketing-coordinator-center-dc-washington</t>
+  </si>
+  <si>
+    <t>Registered Nurse</t>
+  </si>
+  <si>
+    <t>Upper Manhattan Mental Health Center, Inc.</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 109100.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d2fccb1657940a6b77485731a406468-registered-nurse-upper-manhattan-mental-health-center-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Haymarket Center</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27141ad7d000410ea824849a3770a17d-senior-accountant-haymarket-center-chicago</t>
+  </si>
+  <si>
+    <t>Senior Fellow, Energy and Environment</t>
+  </si>
+  <si>
+    <t>R Street Institute</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91b62a098b364f159c510a5dda714b48-senior-fellow-energy-and-environment-r-street-institute-washington</t>
+  </si>
+  <si>
+    <t>Senior Grants Manager</t>
+  </si>
+  <si>
+    <t>Miami Waterkeeper</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Water Sanitation, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa98f2fc29324e06aadf53f97261a4fb-senior-grants-manager-miami-waterkeeper-miami</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Vermont Afghan Alliance Incorporated</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfbaaa39e1794221845270ed22f008df-staff-attorney-vermont-afghan-alliance-incorporated-burlington</t>
+  </si>
+  <si>
+    <t>Legal Aid Society of Eastern Virginia</t>
+  </si>
+  <si>
+    <t>Norfolk, Virginia</t>
+  </si>
+  <si>
+    <t>USD 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42f210cefb1340eeb41bbf414a4c07bc-staff-attorney-legal-aid-society-of-eastern-virginia-norfolk</t>
+  </si>
+  <si>
+    <t>Team Lead Procurement HQ &amp; Internal Services</t>
+  </si>
+  <si>
+    <t>Bonn, Nordrhein-Westfalen, DE</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afe0fdbce0a742cfb900a238690e369f-team-lead-procurement-hq-internal-services-welthungerhilfe-bonn</t>
+  </si>
+  <si>
+    <t>Technology Coordinator</t>
+  </si>
+  <si>
+    <t>Travis Manion Foundation</t>
+  </si>
+  <si>
+    <t>Job Workplace, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99eb9c62f8b24fddb5df00435ec4245b-technology-coordinator-travis-manion-foundation-doylestown</t>
+  </si>
+  <si>
+    <t>Temporary Workers' Rights Staff Attorney</t>
+  </si>
+  <si>
+    <t>TakeRoot Justice</t>
+  </si>
+  <si>
+    <t>USD 46.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75020a24c0dc4a12af7dc475e39a1577-temporary-workers-rights-staff-attorney-takeroot-justice-new-york</t>
+  </si>
+  <si>
+    <t>Training Coordinator</t>
+  </si>
+  <si>
+    <t>Animal Care Centers of NYC</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 26.44 - 26.44/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b53bda3599e1474bbf4cb765c97b9d8d-training-coordinator-animal-care-centers-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Vice President of Programs</t>
+  </si>
+  <si>
+    <t>Prevent Child Abuse - New Jersey</t>
+  </si>
+  <si>
+    <t>North Brunswick Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdd4d5b920e546578b65ff7e755dd7c3-vice-president-of-programs-prevent-child-abuse-new-jersey-north-brunswick-township</t>
+  </si>
+  <si>
+    <t>Vice President, Strategy and Planning</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>USD 156409.67 - 181500.22/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4039a634179e444d8d135c56a9b4c11d-vice-president-strategy-and-planning-the-oakland-zoo-oakland</t>
+  </si>
+  <si>
+    <t>ACADEMIC COORDINATOR I</t>
+  </si>
+  <si>
+    <t>STUDENT FARM ECOLOGICAL GARDEN MANAGER AND EDUCATOR - University of California</t>
+  </si>
+  <si>
+    <t>Davis, California</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74138419</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE AND DATA SERVICES COORDINATOR</t>
+  </si>
+  <si>
+    <t>PART TIME - NOFA MASS</t>
+  </si>
+  <si>
+    <t>Remote, Massachusetts</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74151861</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE COORDINATOR</t>
+  </si>
+  <si>
+    <t>EXTENSION STATE OFFICE - University of New Hampshire</t>
+  </si>
+  <si>
+    <t>Durham, New Hampshire</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74168969</t>
+  </si>
+  <si>
+    <t>ASSISTANT FARMER</t>
+  </si>
+  <si>
+    <t>Round the Bend Farm</t>
+  </si>
+  <si>
+    <t>South Dartmouth, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74121311</t>
+  </si>
+  <si>
+    <t>ASSISTANT PROFESSOR</t>
+  </si>
+  <si>
+    <t>VEGETABLE PRODUCTION SYSTEMS - Cornell University</t>
+  </si>
+  <si>
+    <t>Geneva, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74160415</t>
+  </si>
+  <si>
+    <t>ASSOCIATE DIRECTOR OF ACCOUNTING</t>
+  </si>
+  <si>
+    <t>Painterland Sisters</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74156749</t>
+  </si>
+  <si>
+    <t>CAMPAIGN MANAGER</t>
+  </si>
+  <si>
+    <t>FOOD SAFETY - Center for Science in the Public Interest</t>
+  </si>
+  <si>
+    <t>Washington DC or Remote Office in DC, Washington D</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74112757</t>
+  </si>
+  <si>
+    <t>CLIMATE SMART AGRICULTURE TECHNICAL ASSISTANCE COORDINATOR</t>
+  </si>
+  <si>
+    <t>Bakersfield, California</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Conservation Job Board</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74157971</t>
+  </si>
+  <si>
+    <t>COMMUNICATIONS AND DEVELOPMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74153083</t>
+  </si>
+  <si>
+    <t>COMMUNICATIONS ASSOCIATE</t>
+  </si>
+  <si>
+    <t>PART-TIME - Rhode Island Food Policy Council</t>
+  </si>
+  <si>
+    <t>Remote, must be based in Rhode Island or Massachus</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74146973</t>
+  </si>
+  <si>
+    <t>COMMUNICATIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>Friends of the Mississippi River</t>
+  </si>
+  <si>
+    <t>St Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74145751</t>
+  </si>
+  <si>
+    <t>CONTRACT GRANT WRITER AND GRANT DEVELOPMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>Mezclada</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74159193</t>
+  </si>
+  <si>
+    <t>CROPPING SYSTEMS RESEARCH COORDINATOR</t>
+  </si>
+  <si>
+    <t>Practical Farmers of Iowa</t>
+  </si>
+  <si>
+    <t>Ames, Iowa</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74148195</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>Lower Columbia School Gardens</t>
+  </si>
+  <si>
+    <t>Cowlitz County, Washington</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74110313</t>
+  </si>
+  <si>
+    <t>Blue Ridge Women in Agriculture</t>
+  </si>
+  <si>
+    <t>Boone, North Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74144529</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL PROGRAM OFFICER</t>
+  </si>
+  <si>
+    <t>CLIMATE AND AGRICULTURE - Patagonia Provisions</t>
+  </si>
+  <si>
+    <t>Ventura, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74118867</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Ohio Farm Bureau Foundation</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74132309</t>
+  </si>
+  <si>
+    <t>FARM APPRENTICE</t>
+  </si>
+  <si>
+    <t>Phillies Bridge Farm Project</t>
+  </si>
+  <si>
+    <t>New Paltz, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74111535</t>
+  </si>
+  <si>
+    <t>FARMER ADVOCATE</t>
+  </si>
+  <si>
+    <t>Kearsarge Food Hub</t>
+  </si>
+  <si>
+    <t>Greater Kearsarge Area, New Hampshire</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74162859</t>
+  </si>
+  <si>
+    <t>FINANCE DIRECTOR OF COUNTY OPERATIONS</t>
+  </si>
+  <si>
+    <t>Ohio Farm Bureau</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74133531</t>
+  </si>
+  <si>
+    <t>FOOD AND AGRICULTURE LLM FELLOW</t>
+  </si>
+  <si>
+    <t>Vermont Law and Graduate School</t>
+  </si>
+  <si>
+    <t>South Royalton, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74166525</t>
+  </si>
+  <si>
+    <t>GARDEN ASSISTANT</t>
+  </si>
+  <si>
+    <t>Brays Island</t>
+  </si>
+  <si>
+    <t>Sheldon, South Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74116423</t>
+  </si>
+  <si>
+    <t>GUEST RELATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Blue Hill at Stone Barns</t>
+  </si>
+  <si>
+    <t>Tarrytown, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74139641</t>
+  </si>
+  <si>
+    <t>HEAD OF AGRICULTURAL FOOD RESCUE</t>
+  </si>
+  <si>
+    <t>Sharing Excess</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74120089</t>
+  </si>
+  <si>
+    <t>LAND ACCESS PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>RAFI</t>
+  </si>
+  <si>
+    <t>Remote with priority given to applicants based in</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74161637</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>ASSOCIATE - DIRECTOR - DIRECTOR PUBLIC POLICY - National Association of State Departments of Agriculture</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74167747</t>
+  </si>
+  <si>
+    <t>MANAGER FOR THE FAIRCHILD DAIRY TEACHING AND RESEARCH CENTER</t>
+  </si>
+  <si>
+    <t>University of New Hampshire</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74164081</t>
+  </si>
+  <si>
+    <t>MEAL EXPEDITER AND PACKAGER</t>
+  </si>
+  <si>
+    <t>Open Arms of Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74140863</t>
+  </si>
+  <si>
+    <t>NEW YORK STATE SCHOOL FOOD OPERATIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74137197</t>
+  </si>
+  <si>
+    <t>NUTRIENT MANAGEMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>Maryland Department of Agriculture</t>
+  </si>
+  <si>
+    <t>Frederick, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74127421</t>
+  </si>
+  <si>
+    <t>NUTRITION AND FOOD SYSTEMS SPECIALIST</t>
+  </si>
+  <si>
+    <t>TERM-LIMITED - State of Colorado</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74115201</t>
+  </si>
+  <si>
+    <t>OUTREACH PROGRAMS ADMINISTRATOR</t>
+  </si>
+  <si>
+    <t>TRAINING AND TECHNICAL ASSISTANCE - HUNGER SOLUTIONS INSTITUTE - Auburn University</t>
+  </si>
+  <si>
+    <t>Auburn, Alabama</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74113979</t>
+  </si>
+  <si>
+    <t>PHD GRADUATE RESEARCH ASSISTANT â€“ AQUATIC ANIMAL HEALTH AND SUSTAINABLE AQUACULTURE</t>
+  </si>
+  <si>
+    <t>University of Georgia</t>
+  </si>
+  <si>
+    <t>Athens, Georgia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74124977</t>
+  </si>
+  <si>
+    <t>POULTRY CERTIFICATION COORDINATOR SPECIALIST</t>
+  </si>
+  <si>
+    <t>NOFA NY</t>
+  </si>
+  <si>
+    <t>Remote, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74150639</t>
+  </si>
+  <si>
+    <t>PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>FairShare CSA Coalition</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74123755</t>
+  </si>
+  <si>
+    <t>New Roots Institute</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74154305</t>
+  </si>
+  <si>
+    <t>PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>USDA ADVANCING MARKETS FOR PRODUCERS - Winrock International</t>
+  </si>
+  <si>
+    <t>Fully remote, preference given to applicants resid</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74126199</t>
+  </si>
+  <si>
+    <t>PROGRAM OPERATION AND DATA MANAGER</t>
+  </si>
+  <si>
+    <t>Community Harvest of Central Vermont</t>
+  </si>
+  <si>
+    <t>Berlin, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74143307</t>
+  </si>
+  <si>
+    <t>RESEARCH MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74149417</t>
+  </si>
+  <si>
+    <t>SEAFOOD BUSINESS AND MARKET DEVELOPMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>North Carolina State University</t>
+  </si>
+  <si>
+    <t>Raleigh-Durham-Chapel Hill Area, North Carolina</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74131087</t>
+  </si>
+  <si>
+    <t>SEAFOOD MARKETING MANAGER</t>
+  </si>
+  <si>
+    <t>Anne Arundel, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74128643</t>
+  </si>
+  <si>
+    <t>SEASONAL FARMER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74122533</t>
+  </si>
+  <si>
+    <t>SENIOR PROGRAM OFFICER</t>
+  </si>
+  <si>
+    <t>FOOD NUTRITION AND AGRICULTURE PROGRAM - National Academies of Sciences Engineering and Medicine</t>
+  </si>
+  <si>
+    <t>Washington DC Hybrid, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74117645</t>
+  </si>
+  <si>
+    <t>SENIOR SPECIALIST</t>
+  </si>
+  <si>
+    <t>OPERATIONS - Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74134753</t>
+  </si>
+  <si>
+    <t>SPECIALIST</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74135975</t>
+  </si>
+  <si>
+    <t>VEGETABLE MANAGER</t>
+  </si>
+  <si>
+    <t>Farms Work Wonders</t>
+  </si>
+  <si>
+    <t>Wardensville, West Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74142085</t>
+  </si>
+  <si>
+    <t>VETERINARY LABRATORY OPERATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Wicomico, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74129865</t>
+  </si>
+  <si>
+    <t>VISITING EXTENSION EDUCATOR</t>
+  </si>
+  <si>
+    <t>COMMUNITY AND ECONOMIC DEVELOPMENT - COMMUNITY DEVELOPMENT AND PLANNING - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>East Saint Louis, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=74155527</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1992,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2018,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2400,925 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F26" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" t="s">
+        <v>163</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32" t="s">
+        <v>169</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>174</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" t="s">
+        <v>181</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>177</v>
+      </c>
+      <c r="B35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" t="s">
+        <v>198</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3365,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3439,1234 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" t="s">
+        <v>247</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" t="s">
+        <v>263</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" t="s">
+        <v>268</v>
+      </c>
+      <c r="F11" t="s">
+        <v>269</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B12" t="s">
+        <v>272</v>
+      </c>
+      <c r="C12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" t="s">
+        <v>274</v>
+      </c>
+      <c r="F12" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C13" t="s">
+        <v>277</v>
+      </c>
+      <c r="D13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" t="s">
+        <v>262</v>
+      </c>
+      <c r="F13" t="s">
+        <v>278</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" t="s">
+        <v>283</v>
+      </c>
+      <c r="F14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F16" t="s">
+        <v>294</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" t="s">
+        <v>298</v>
+      </c>
+      <c r="F17" t="s">
+        <v>299</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B18" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" t="s">
+        <v>303</v>
+      </c>
+      <c r="D18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" t="s">
+        <v>304</v>
+      </c>
+      <c r="F18" t="s">
+        <v>305</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" t="s">
+        <v>310</v>
+      </c>
+      <c r="F19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" t="s">
+        <v>215</v>
+      </c>
+      <c r="E20" t="s">
+        <v>315</v>
+      </c>
+      <c r="F20" t="s">
+        <v>316</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>318</v>
+      </c>
+      <c r="C21" t="s">
+        <v>319</v>
+      </c>
+      <c r="D21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" t="s">
+        <v>320</v>
+      </c>
+      <c r="F21" t="s">
+        <v>288</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>322</v>
+      </c>
+      <c r="C22" t="s">
+        <v>323</v>
+      </c>
+      <c r="D22" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" t="s">
+        <v>324</v>
+      </c>
+      <c r="F22" t="s">
+        <v>325</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" t="s">
+        <v>215</v>
+      </c>
+      <c r="E23" t="s">
+        <v>329</v>
+      </c>
+      <c r="F23" t="s">
+        <v>288</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>331</v>
+      </c>
+      <c r="B24" t="s">
+        <v>332</v>
+      </c>
+      <c r="C24" t="s">
+        <v>333</v>
+      </c>
+      <c r="D24" t="s">
+        <v>215</v>
+      </c>
+      <c r="E24" t="s">
+        <v>334</v>
+      </c>
+      <c r="F24" t="s">
+        <v>335</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" t="s">
+        <v>339</v>
+      </c>
+      <c r="D25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F25" t="s">
+        <v>288</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>341</v>
+      </c>
+      <c r="B26" t="s">
+        <v>342</v>
+      </c>
+      <c r="C26" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26" t="s">
+        <v>343</v>
+      </c>
+      <c r="F26" t="s">
+        <v>344</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>346</v>
+      </c>
+      <c r="B27" t="s">
+        <v>347</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
+        <v>215</v>
+      </c>
+      <c r="E27" t="s">
+        <v>348</v>
+      </c>
+      <c r="F27" t="s">
+        <v>349</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" t="s">
+        <v>352</v>
+      </c>
+      <c r="F28" t="s">
+        <v>353</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>355</v>
+      </c>
+      <c r="B29" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" t="s">
+        <v>215</v>
+      </c>
+      <c r="E29" t="s">
+        <v>357</v>
+      </c>
+      <c r="F29" t="s">
+        <v>358</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" t="s">
+        <v>361</v>
+      </c>
+      <c r="C30" t="s">
+        <v>362</v>
+      </c>
+      <c r="D30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" t="s">
+        <v>363</v>
+      </c>
+      <c r="F30" t="s">
+        <v>364</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>366</v>
+      </c>
+      <c r="B31" t="s">
+        <v>367</v>
+      </c>
+      <c r="C31" t="s">
+        <v>368</v>
+      </c>
+      <c r="D31" t="s">
+        <v>369</v>
+      </c>
+      <c r="E31" t="s">
+        <v>370</v>
+      </c>
+      <c r="F31" t="s">
+        <v>335</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>372</v>
+      </c>
+      <c r="B32" t="s">
+        <v>373</v>
+      </c>
+      <c r="C32" t="s">
+        <v>374</v>
+      </c>
+      <c r="D32" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" t="s">
+        <v>375</v>
+      </c>
+      <c r="F32" t="s">
+        <v>376</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" t="s">
+        <v>379</v>
+      </c>
+      <c r="C33" t="s">
+        <v>380</v>
+      </c>
+      <c r="D33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E33" t="s">
+        <v>381</v>
+      </c>
+      <c r="F33" t="s">
+        <v>382</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>384</v>
+      </c>
+      <c r="B34" t="s">
+        <v>385</v>
+      </c>
+      <c r="C34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D34" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" t="s">
+        <v>386</v>
+      </c>
+      <c r="F34" t="s">
+        <v>311</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>388</v>
+      </c>
+      <c r="B35" t="s">
+        <v>389</v>
+      </c>
+      <c r="C35" t="s">
+        <v>380</v>
+      </c>
+      <c r="D35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" t="s">
+        <v>390</v>
+      </c>
+      <c r="F35" t="s">
+        <v>391</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>393</v>
+      </c>
+      <c r="B36" t="s">
+        <v>394</v>
+      </c>
+      <c r="C36" t="s">
+        <v>395</v>
+      </c>
+      <c r="D36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" t="s">
+        <v>375</v>
+      </c>
+      <c r="F36" t="s">
+        <v>396</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>398</v>
+      </c>
+      <c r="B37" t="s">
+        <v>399</v>
+      </c>
+      <c r="C37" t="s">
+        <v>400</v>
+      </c>
+      <c r="D37" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" t="s">
+        <v>401</v>
+      </c>
+      <c r="F37" t="s">
+        <v>288</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>403</v>
+      </c>
+      <c r="B38" t="s">
+        <v>404</v>
+      </c>
+      <c r="C38" t="s">
+        <v>303</v>
+      </c>
+      <c r="D38" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" t="s">
+        <v>405</v>
+      </c>
+      <c r="F38" t="s">
+        <v>406</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>408</v>
+      </c>
+      <c r="B39" t="s">
+        <v>409</v>
+      </c>
+      <c r="C39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D39" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F39" t="s">
+        <v>412</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" t="s">
+        <v>404</v>
+      </c>
+      <c r="C40" t="s">
+        <v>303</v>
+      </c>
+      <c r="D40" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" t="s">
+        <v>415</v>
+      </c>
+      <c r="F40" t="s">
+        <v>406</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>417</v>
+      </c>
+      <c r="B41" t="s">
+        <v>418</v>
+      </c>
+      <c r="C41" t="s">
+        <v>245</v>
+      </c>
+      <c r="D41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E41" t="s">
+        <v>419</v>
+      </c>
+      <c r="F41" t="s">
+        <v>420</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>422</v>
+      </c>
+      <c r="B42" t="s">
+        <v>423</v>
+      </c>
+      <c r="C42" t="s">
+        <v>214</v>
+      </c>
+      <c r="D42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E42" t="s">
+        <v>424</v>
+      </c>
+      <c r="F42" t="s">
+        <v>425</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>427</v>
+      </c>
+      <c r="B43" t="s">
+        <v>428</v>
+      </c>
+      <c r="C43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" t="s">
+        <v>215</v>
+      </c>
+      <c r="E43" t="s">
+        <v>429</v>
+      </c>
+      <c r="F43" t="s">
+        <v>430</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>432</v>
+      </c>
+      <c r="B44" t="s">
+        <v>433</v>
+      </c>
+      <c r="C44" t="s">
+        <v>434</v>
+      </c>
+      <c r="D44" t="s">
+        <v>215</v>
+      </c>
+      <c r="E44" t="s">
+        <v>435</v>
+      </c>
+      <c r="F44" t="s">
+        <v>436</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>438</v>
+      </c>
+      <c r="B45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C45" t="s">
+        <v>440</v>
+      </c>
+      <c r="D45" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" t="s">
+        <v>441</v>
+      </c>
+      <c r="F45" t="s">
+        <v>263</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>438</v>
+      </c>
+      <c r="B46" t="s">
+        <v>443</v>
+      </c>
+      <c r="C46" t="s">
+        <v>444</v>
+      </c>
+      <c r="D46" t="s">
+        <v>215</v>
+      </c>
+      <c r="E46" t="s">
+        <v>445</v>
+      </c>
+      <c r="F46" t="s">
+        <v>288</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>447</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>448</v>
+      </c>
+      <c r="D47" t="s">
+        <v>227</v>
+      </c>
+      <c r="E47" t="s">
+        <v>288</v>
+      </c>
+      <c r="F47" t="s">
+        <v>289</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>450</v>
+      </c>
+      <c r="B48" t="s">
+        <v>451</v>
+      </c>
+      <c r="C48" t="s">
+        <v>207</v>
+      </c>
+      <c r="D48" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" t="s">
+        <v>452</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>454</v>
+      </c>
+      <c r="B49" t="s">
+        <v>455</v>
+      </c>
+      <c r="C49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D49" t="s">
+        <v>369</v>
+      </c>
+      <c r="E49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F49" t="s">
+        <v>457</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>459</v>
+      </c>
+      <c r="B50" t="s">
+        <v>460</v>
+      </c>
+      <c r="C50" t="s">
+        <v>461</v>
+      </c>
+      <c r="D50" t="s">
+        <v>215</v>
+      </c>
+      <c r="E50" t="s">
+        <v>462</v>
+      </c>
+      <c r="F50" t="s">
+        <v>463</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B51" t="s">
+        <v>466</v>
+      </c>
+      <c r="C51" t="s">
+        <v>467</v>
+      </c>
+      <c r="D51" t="s">
+        <v>215</v>
+      </c>
+      <c r="E51" t="s">
+        <v>468</v>
+      </c>
+      <c r="F51" t="s">
+        <v>469</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>471</v>
+      </c>
+      <c r="B52" t="s">
+        <v>238</v>
+      </c>
+      <c r="C52" t="s">
+        <v>472</v>
+      </c>
+      <c r="D52" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" t="s">
+        <v>473</v>
+      </c>
+      <c r="F52" t="s">
+        <v>241</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -562,7 +4674,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -601,8 +4713,1165 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4" t="s">
+        <v>483</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>489</v>
+      </c>
+      <c r="B5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C5" t="s">
+        <v>491</v>
+      </c>
+      <c r="D5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" t="s">
+        <v>478</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>497</v>
+      </c>
+      <c r="B7" t="s">
+        <v>498</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" t="s">
+        <v>483</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>506</v>
+      </c>
+      <c r="D9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F9" t="s">
+        <v>507</v>
+      </c>
+      <c r="G9" t="s">
+        <v>508</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>510</v>
+      </c>
+      <c r="B10" t="s">
+        <v>481</v>
+      </c>
+      <c r="C10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F10" t="s">
+        <v>511</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>513</v>
+      </c>
+      <c r="B11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C11" t="s">
+        <v>515</v>
+      </c>
+      <c r="D11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" t="s">
+        <v>516</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B12" t="s">
+        <v>519</v>
+      </c>
+      <c r="C12" t="s">
+        <v>520</v>
+      </c>
+      <c r="D12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F12" t="s">
+        <v>516</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>522</v>
+      </c>
+      <c r="B13" t="s">
+        <v>523</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>288</v>
+      </c>
+      <c r="E13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13" t="s">
+        <v>511</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>525</v>
+      </c>
+      <c r="B14" t="s">
+        <v>526</v>
+      </c>
+      <c r="C14" t="s">
+        <v>527</v>
+      </c>
+      <c r="D14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" t="s">
+        <v>288</v>
+      </c>
+      <c r="F14" t="s">
+        <v>528</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>530</v>
+      </c>
+      <c r="B15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C15" t="s">
+        <v>532</v>
+      </c>
+      <c r="D15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15" t="s">
+        <v>511</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" t="s">
+        <v>534</v>
+      </c>
+      <c r="C16" t="s">
+        <v>535</v>
+      </c>
+      <c r="D16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16" t="s">
+        <v>511</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B17" t="s">
+        <v>538</v>
+      </c>
+      <c r="C17" t="s">
+        <v>539</v>
+      </c>
+      <c r="D17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E17" t="s">
+        <v>288</v>
+      </c>
+      <c r="F17" t="s">
+        <v>478</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B18" t="s">
+        <v>542</v>
+      </c>
+      <c r="C18" t="s">
+        <v>543</v>
+      </c>
+      <c r="D18" t="s">
+        <v>288</v>
+      </c>
+      <c r="E18" t="s">
+        <v>288</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B19" t="s">
+        <v>546</v>
+      </c>
+      <c r="C19" t="s">
+        <v>547</v>
+      </c>
+      <c r="D19" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" t="s">
+        <v>288</v>
+      </c>
+      <c r="F19" t="s">
+        <v>478</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>549</v>
+      </c>
+      <c r="B20" t="s">
+        <v>550</v>
+      </c>
+      <c r="C20" t="s">
+        <v>551</v>
+      </c>
+      <c r="D20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E20" t="s">
+        <v>288</v>
+      </c>
+      <c r="F20" t="s">
+        <v>478</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>553</v>
+      </c>
+      <c r="B21" t="s">
+        <v>554</v>
+      </c>
+      <c r="C21" t="s">
+        <v>543</v>
+      </c>
+      <c r="D21" t="s">
+        <v>288</v>
+      </c>
+      <c r="E21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" t="s">
+        <v>483</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>556</v>
+      </c>
+      <c r="B22" t="s">
+        <v>557</v>
+      </c>
+      <c r="C22" t="s">
+        <v>558</v>
+      </c>
+      <c r="D22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E22" t="s">
+        <v>288</v>
+      </c>
+      <c r="F22" t="s">
+        <v>528</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>560</v>
+      </c>
+      <c r="B23" t="s">
+        <v>561</v>
+      </c>
+      <c r="C23" t="s">
+        <v>562</v>
+      </c>
+      <c r="D23" t="s">
+        <v>288</v>
+      </c>
+      <c r="E23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F23" t="s">
+        <v>478</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>564</v>
+      </c>
+      <c r="B24" t="s">
+        <v>565</v>
+      </c>
+      <c r="C24" t="s">
+        <v>566</v>
+      </c>
+      <c r="D24" t="s">
+        <v>288</v>
+      </c>
+      <c r="E24" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" t="s">
+        <v>478</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>568</v>
+      </c>
+      <c r="B25" t="s">
+        <v>569</v>
+      </c>
+      <c r="C25" t="s">
+        <v>570</v>
+      </c>
+      <c r="D25" t="s">
+        <v>288</v>
+      </c>
+      <c r="E25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F25" t="s">
+        <v>478</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>572</v>
+      </c>
+      <c r="B26" t="s">
+        <v>573</v>
+      </c>
+      <c r="C26" t="s">
+        <v>574</v>
+      </c>
+      <c r="D26" t="s">
+        <v>288</v>
+      </c>
+      <c r="E26" t="s">
+        <v>288</v>
+      </c>
+      <c r="F26" t="s">
+        <v>503</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>576</v>
+      </c>
+      <c r="B27" t="s">
+        <v>577</v>
+      </c>
+      <c r="C27" t="s">
+        <v>578</v>
+      </c>
+      <c r="D27" t="s">
+        <v>288</v>
+      </c>
+      <c r="E27" t="s">
+        <v>288</v>
+      </c>
+      <c r="F27" t="s">
+        <v>503</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>580</v>
+      </c>
+      <c r="B28" t="s">
+        <v>581</v>
+      </c>
+      <c r="C28" t="s">
+        <v>487</v>
+      </c>
+      <c r="D28" t="s">
+        <v>288</v>
+      </c>
+      <c r="E28" t="s">
+        <v>288</v>
+      </c>
+      <c r="F28" t="s">
+        <v>478</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>583</v>
+      </c>
+      <c r="B29" t="s">
+        <v>584</v>
+      </c>
+      <c r="C29" t="s">
+        <v>520</v>
+      </c>
+      <c r="D29" t="s">
+        <v>288</v>
+      </c>
+      <c r="E29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F29" t="s">
+        <v>478</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>586</v>
+      </c>
+      <c r="B30" t="s">
+        <v>587</v>
+      </c>
+      <c r="C30" t="s">
+        <v>245</v>
+      </c>
+      <c r="D30" t="s">
+        <v>288</v>
+      </c>
+      <c r="E30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F30" t="s">
+        <v>478</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>589</v>
+      </c>
+      <c r="B31" t="s">
+        <v>590</v>
+      </c>
+      <c r="C31" t="s">
+        <v>591</v>
+      </c>
+      <c r="D31" t="s">
+        <v>288</v>
+      </c>
+      <c r="E31" t="s">
+        <v>288</v>
+      </c>
+      <c r="F31" t="s">
+        <v>478</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>593</v>
+      </c>
+      <c r="B32" t="s">
+        <v>594</v>
+      </c>
+      <c r="C32" t="s">
+        <v>380</v>
+      </c>
+      <c r="D32" t="s">
+        <v>288</v>
+      </c>
+      <c r="E32" t="s">
+        <v>288</v>
+      </c>
+      <c r="F32" t="s">
+        <v>478</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>596</v>
+      </c>
+      <c r="B33" t="s">
+        <v>597</v>
+      </c>
+      <c r="C33" t="s">
+        <v>598</v>
+      </c>
+      <c r="D33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E33" t="s">
+        <v>288</v>
+      </c>
+      <c r="F33" t="s">
+        <v>478</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>600</v>
+      </c>
+      <c r="B34" t="s">
+        <v>601</v>
+      </c>
+      <c r="C34" t="s">
+        <v>602</v>
+      </c>
+      <c r="D34" t="s">
+        <v>288</v>
+      </c>
+      <c r="E34" t="s">
+        <v>288</v>
+      </c>
+      <c r="F34" t="s">
+        <v>528</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>604</v>
+      </c>
+      <c r="B35" t="s">
+        <v>605</v>
+      </c>
+      <c r="C35" t="s">
+        <v>606</v>
+      </c>
+      <c r="D35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E35" t="s">
+        <v>288</v>
+      </c>
+      <c r="F35" t="s">
+        <v>478</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>608</v>
+      </c>
+      <c r="B36" t="s">
+        <v>609</v>
+      </c>
+      <c r="C36" t="s">
+        <v>610</v>
+      </c>
+      <c r="D36" t="s">
+        <v>288</v>
+      </c>
+      <c r="E36" t="s">
+        <v>288</v>
+      </c>
+      <c r="F36" t="s">
+        <v>478</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>608</v>
+      </c>
+      <c r="B37" t="s">
+        <v>612</v>
+      </c>
+      <c r="C37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" t="s">
+        <v>288</v>
+      </c>
+      <c r="E37" t="s">
+        <v>288</v>
+      </c>
+      <c r="F37" t="s">
+        <v>478</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>614</v>
+      </c>
+      <c r="B38" t="s">
+        <v>615</v>
+      </c>
+      <c r="C38" t="s">
+        <v>616</v>
+      </c>
+      <c r="D38" t="s">
+        <v>288</v>
+      </c>
+      <c r="E38" t="s">
+        <v>288</v>
+      </c>
+      <c r="F38" t="s">
+        <v>478</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>618</v>
+      </c>
+      <c r="B39" t="s">
+        <v>619</v>
+      </c>
+      <c r="C39" t="s">
+        <v>620</v>
+      </c>
+      <c r="D39" t="s">
+        <v>288</v>
+      </c>
+      <c r="E39" t="s">
+        <v>288</v>
+      </c>
+      <c r="F39" t="s">
+        <v>478</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>622</v>
+      </c>
+      <c r="B40" t="s">
+        <v>526</v>
+      </c>
+      <c r="C40" t="s">
+        <v>527</v>
+      </c>
+      <c r="D40" t="s">
+        <v>288</v>
+      </c>
+      <c r="E40" t="s">
+        <v>288</v>
+      </c>
+      <c r="F40" t="s">
+        <v>528</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>624</v>
+      </c>
+      <c r="B41" t="s">
+        <v>625</v>
+      </c>
+      <c r="C41" t="s">
+        <v>626</v>
+      </c>
+      <c r="D41" t="s">
+        <v>288</v>
+      </c>
+      <c r="E41" t="s">
+        <v>288</v>
+      </c>
+      <c r="F41" t="s">
+        <v>627</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>629</v>
+      </c>
+      <c r="B42" t="s">
+        <v>590</v>
+      </c>
+      <c r="C42" t="s">
+        <v>630</v>
+      </c>
+      <c r="D42" t="s">
+        <v>288</v>
+      </c>
+      <c r="E42" t="s">
+        <v>288</v>
+      </c>
+      <c r="F42" t="s">
+        <v>627</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>632</v>
+      </c>
+      <c r="B43" t="s">
+        <v>490</v>
+      </c>
+      <c r="C43" t="s">
+        <v>491</v>
+      </c>
+      <c r="D43" t="s">
+        <v>288</v>
+      </c>
+      <c r="E43" t="s">
+        <v>288</v>
+      </c>
+      <c r="F43" t="s">
+        <v>478</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>634</v>
+      </c>
+      <c r="B44" t="s">
+        <v>635</v>
+      </c>
+      <c r="C44" t="s">
+        <v>636</v>
+      </c>
+      <c r="D44" t="s">
+        <v>288</v>
+      </c>
+      <c r="E44" t="s">
+        <v>288</v>
+      </c>
+      <c r="F44" t="s">
+        <v>478</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>638</v>
+      </c>
+      <c r="B45" t="s">
+        <v>639</v>
+      </c>
+      <c r="C45" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" t="s">
+        <v>288</v>
+      </c>
+      <c r="E45" t="s">
+        <v>288</v>
+      </c>
+      <c r="F45" t="s">
+        <v>478</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>641</v>
+      </c>
+      <c r="B46" t="s">
+        <v>639</v>
+      </c>
+      <c r="C46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" t="s">
+        <v>288</v>
+      </c>
+      <c r="E46" t="s">
+        <v>288</v>
+      </c>
+      <c r="F46" t="s">
+        <v>478</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>643</v>
+      </c>
+      <c r="B47" t="s">
+        <v>644</v>
+      </c>
+      <c r="C47" t="s">
+        <v>645</v>
+      </c>
+      <c r="D47" t="s">
+        <v>288</v>
+      </c>
+      <c r="E47" t="s">
+        <v>288</v>
+      </c>
+      <c r="F47" t="s">
+        <v>478</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>647</v>
+      </c>
+      <c r="B48" t="s">
+        <v>590</v>
+      </c>
+      <c r="C48" t="s">
+        <v>648</v>
+      </c>
+      <c r="D48" t="s">
+        <v>288</v>
+      </c>
+      <c r="E48" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" t="s">
+        <v>478</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>650</v>
+      </c>
+      <c r="B49" t="s">
+        <v>651</v>
+      </c>
+      <c r="C49" t="s">
+        <v>652</v>
+      </c>
+      <c r="D49" t="s">
+        <v>288</v>
+      </c>
+      <c r="E49" t="s">
+        <v>288</v>
+      </c>
+      <c r="F49" t="s">
+        <v>478</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-21.xlsx
+++ b/docs/xlsx/jobs-2026-10-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="874">
   <si>
     <t>Title</t>
   </si>
@@ -688,6 +688,108 @@
     <t>https://www.idealist.org/en/consultant-job/e8e6bfccad584ca5ba2261bd615fbd33-advisor-salesforce-solutions-bme-strategies-north-andover</t>
   </si>
   <si>
+    <t>Assistant Vice President, Consulting (Northeast)</t>
+  </si>
+  <si>
+    <t>Primary Care Development Corporation</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 193000.00 - 227000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3347f1ea58424967b7e6b38ced16e0c7-assistant-vice-president-consulting-northeast-primary-care-development-corporation-new-york</t>
+  </si>
+  <si>
+    <t>Associate Director of Development</t>
+  </si>
+  <si>
+    <t>Essie Justice Group</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cbe0e9c0c2041428626ed38ebdd2203-associate-director-of-development-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31d7be2c879847658ba7769b8f70252c-associate-director-of-development-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>Associate Director of Organizing</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b90734ea170425db47650fe3ae1577d-associate-director-of-organizing-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Attorney (Homelessness Prevention) – Restoring Communities Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>South Gate, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95613.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6aac58bd689459196ad80100c805bbd-attorney-homelessness-prevention-restoring-communities-workgroup-legal-aid-foundation-of-los-angeles-south-gate</t>
+  </si>
+  <si>
+    <t>Beyond Housing- HUD Certified Housing Counselor ( St. Louis, MO)</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fbdd3c8ced143d8888d9a7488b69589-beyond-housing-hud-certified-housing-counselor-st-louis-mo-neighborworks-affiliates-st-louis</t>
+  </si>
+  <si>
+    <t>Bilingual (Spanish) Case Manager</t>
+  </si>
+  <si>
+    <t>Partnerships for Trauma Recovery</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dffc48f5664540d3bac3865ccd031b01-bilingual-spanish-case-manager-partnerships-for-trauma-recovery-berkeley</t>
+  </si>
+  <si>
     <t>Business and Cooperative Development Specialist</t>
   </si>
   <si>
@@ -709,6 +811,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a0b8451ecdc547228080debab3028427-business-and-cooperative-development-specialist-masa-bronx</t>
   </si>
   <si>
+    <t>Chief Data Officer (CDO)</t>
+  </si>
+  <si>
+    <t>United Hospital Fund of New York</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 18000.00 - 210000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4242e57189674f33bb55169b40cc713e-chief-data-officer-cdo-united-hospital-fund-of-new-york-new-york</t>
+  </si>
+  <si>
     <t>Chief Executive Officer</t>
   </si>
   <si>
@@ -733,9 +853,6 @@
     <t>The Oakland Zoo</t>
   </si>
   <si>
-    <t>Oakland, California</t>
-  </si>
-  <si>
     <t>USD 189223.00 - 210247.78/year</t>
   </si>
   <si>
@@ -751,9 +868,6 @@
     <t>Healing New York</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 70000.00/year</t>
   </si>
   <si>
@@ -763,6 +877,102 @@
     <t>https://www.idealist.org/en/nonprofit-job/27696f74a8ff4c0e833443a6a4813fe2-child-abuse-prevention-training-specialist-healing-new-york-new-york</t>
   </si>
   <si>
+    <t>Church Building Manager</t>
+  </si>
+  <si>
+    <t>Church of the Covenant</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2ed90c929b5742b6a5bd16cb3e3b36e9-church-building-manager-church-of-the-covenant-boston</t>
+  </si>
+  <si>
+    <t>Civic Engagement Organizer</t>
+  </si>
+  <si>
+    <t>Make the Road States</t>
+  </si>
+  <si>
+    <t>Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>USD 64661.00 - 73913.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05485b3a74ae43e0b3f81ed0fb31c8fb-civic-engagement-organizer-make-the-road-states-lansing</t>
+  </si>
+  <si>
+    <t>Climate Campaign Director</t>
+  </si>
+  <si>
+    <t>Corporate Accountability</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Human Rights Civil Liberties, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1a1bc3b8c694abaa5d2c244e837bae0-climate-campaign-director-corporate-accountability-boston</t>
+  </si>
+  <si>
+    <t>Colorado Grazing Specialist</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Fort Collins, Colorado</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/75f36ee00e6d4a00bbcd8e64355d6151-colorado-grazing-specialist-american-farmland-trust-fort-collins</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8fe594276cb4899a94f84b65d64fffa-communications-manager-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07116c6860da44f392d98d5ed754dc9d-communications-manager-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>Hartford, Connecticut</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b8a93cfc92a4cd2bfd976154cebfa5e-community-organizer-make-the-road-states-hartford</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -778,6 +988,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/f1d88acf4d15438688c94c142a434431-controller-united-jewish-council-of-the-east-side-inc-new-york</t>
   </si>
   <si>
+    <t>Deputy Director</t>
+  </si>
+  <si>
+    <t>Tribal EcoRestoration Alliance</t>
+  </si>
+  <si>
+    <t>Lower Lake, California</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/390cab1ec8dc465e8045e93b504607d0-deputy-director-tribal-ecorestoration-alliance-lower-lake</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Tilth Alliance</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0e36812fc47478ebd0c1fea9317e66e-development-associate-tilth-alliance-seattle</t>
+  </si>
+  <si>
     <t>Development Director</t>
   </si>
   <si>
@@ -829,6 +1075,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c449635aba0e46f3a1b8348bd18cbb30-development-officer-special-events-seeds-access-changes-everything-newark</t>
   </si>
   <si>
+    <t>Director Advocacy and Policy</t>
+  </si>
+  <si>
+    <t>Children's Rights</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a370733572741e6b05de922772c00bd-director-advocacy-and-policy-childrens-rights-new-york</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -856,6 +1117,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/ecb96549bf6240e0ac0c03a971e20132-director-of-development-national-council-for-adoption-alexandria</t>
   </si>
   <si>
+    <t>Director of Labor and Coalition Relations</t>
+  </si>
+  <si>
+    <t>Jewish California</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3d7cfefc22b42d69a87bdaccf107c37-director-of-labor-and-coalition-relations-jewish-california-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Partnerships and Strategic Initiatives</t>
+  </si>
+  <si>
+    <t>American Oversight</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38e10f9120bf404cbe8895ecab2f69c7-director-of-partnerships-and-strategic-initiatives-american-oversight-washington</t>
+  </si>
+  <si>
+    <t>Director of Primary Care Operations Consulting (California based)</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cdf774383014dc0a688f19f5dc70cf2-director-of-primary-care-operations-consulting-california-based-primary-care-development-corporation-new-york</t>
+  </si>
+  <si>
     <t>Director of Workforce Development at Immigrant Family Services Institute</t>
   </si>
   <si>
@@ -880,15 +1183,18 @@
     <t>Kabul, Kabul, AF</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Agriculture, Disaster Relief, Hunger Food Security</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/595f69d9d9834ff89e329cd87159f813-director-programs-afghanistan-welthungerhilfe-kabul</t>
   </si>
   <si>
+    <t>Director, Consulting Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d59b59fb9ce441a8b26af91a3366cfb-director-consulting-operations-primary-care-development-corporation-new-york</t>
+  </si>
+  <si>
     <t>Director, Digital Strategy, Communications</t>
   </si>
   <si>
@@ -904,6 +1210,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/9ef8cdec9f9b47b39f3714e19d5d857f-director-digital-strategy-communications-vera-institute-of-justice-new-york</t>
   </si>
   <si>
+    <t>Director, Member Engagement</t>
+  </si>
+  <si>
+    <t>Southern California Grantmakers</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c359800bb6fc482da51173cfaad19223-director-member-engagement-southern-california-grantmakers-los-angeles</t>
+  </si>
+  <si>
+    <t>Director, Program Administration and Evaluation</t>
+  </si>
+  <si>
+    <t>United Way of New York City</t>
+  </si>
+  <si>
+    <t>USD 80874.00 - 91424.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2efd0e06b30b4bf1a94c0d913cd18597-director-program-administration-and-evaluation-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Director, SAGE Center Harlem</t>
   </si>
   <si>
@@ -937,6 +1273,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/7500654856db481f9639ff441db9143d-director-tax-policy-the-bipartisan-policy-center-washington</t>
   </si>
   <si>
+    <t>Economic Empowerment Program Manager</t>
+  </si>
+  <si>
+    <t>Girls Educational &amp; Mentoring Services, Inc.</t>
+  </si>
+  <si>
+    <t>Children Youth, Sexual Abuse Human Trafficking, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4426f0ae8f6243d88399ac26ce5fc91d-economic-empowerment-program-manager-girls-educational-mentoring-services-inc-new-york</t>
+  </si>
+  <si>
     <t>Employment Coordinator</t>
   </si>
   <si>
@@ -997,6 +1345,18 @@
     <t>https://www.idealist.org/en/job/71190f46e933477896fce5548ff8b951-executive-director-association-of-infant-mental-health-in-tennessee-nashville</t>
   </si>
   <si>
+    <t>Executive Director ISTAT Foundation</t>
+  </si>
+  <si>
+    <t>Smithbucklin</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/bbe7baf30b394a13ac73adcdd18b7dbe-executive-director-istat-foundation-smithbucklin-chicago</t>
+  </si>
+  <si>
     <t>Executive Director, Mattapan Food and Fitness Coalition</t>
   </si>
   <si>
@@ -1027,6 +1387,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/916ca008d93e47adbe17f6ba4ab9db4e-field-representative-central-california-california-federation-of-teachers-fresno</t>
   </si>
   <si>
+    <t>Finance Controller</t>
+  </si>
+  <si>
+    <t>Upper Lake, California</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 44.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef623a2176fa44f9947c1bd30d7ea8fe-finance-controller-tribal-ecorestoration-alliance-upper-lake</t>
+  </si>
+  <si>
     <t>GCCFI Senior Program Manager</t>
   </si>
   <si>
@@ -1039,6 +1411,51 @@
     <t>https://www.idealist.org/en/job/41810ecbcf3b41bf8b53701237e6eb2f-gccfi-senior-program-manager-grand-canyon-conservancy-grand-canyon</t>
   </si>
   <si>
+    <t>Government &amp; Ecosystem Manager</t>
+  </si>
+  <si>
+    <t>Pi Jam Foundation</t>
+  </si>
+  <si>
+    <t>Mumbai, Maharashtra, IN</t>
+  </si>
+  <si>
+    <t>INR 45000.00 - 60000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Communications Access, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f639e136204d46dbae4b7f1f75792f6d-government-ecosystem-manager-pi-jam-foundation-mumbai</t>
+  </si>
+  <si>
+    <t>Grant Accountant</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdcc1dbb877d4383b1f63bbd2cf4de55-grant-accountant-primary-care-development-corporation-new-york</t>
+  </si>
+  <si>
+    <t>Housekeeping and Facilities Tech</t>
+  </si>
+  <si>
+    <t>The Hole in the Wall Gang Fund, Inc.</t>
+  </si>
+  <si>
+    <t>Queenstown, Maryland</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2055f67b16c446c7b435f406c5074d45-housekeeping-and-facilities-tech-the-hole-in-the-wall-gang-fund-inc-queenstown</t>
+  </si>
+  <si>
     <t>Human Resources Operations Manager</t>
   </si>
   <si>
@@ -1069,6 +1486,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2a8dd7c5eb1e4b9a99c2b6a9b3a36004-individual-giving-manager-planned-parenthood-columbia-willamette-portland</t>
   </si>
   <si>
+    <t>Internship Coordinator (Part-time)</t>
+  </si>
+  <si>
+    <t>Cycles of Change</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 30.78 - 30.78/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87bd5b3b4a994fc4a06ef6d6194bb6f6-internship-coordinator-part-time-cycles-of-change-oakland</t>
+  </si>
+  <si>
     <t>Language Justice Program Coordinator</t>
   </si>
   <si>
@@ -1123,9 +1558,6 @@
     <t>Manchester-by-the-Sea, Massachusetts</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 45000.00/year</t>
   </si>
   <si>
@@ -1162,24 +1594,54 @@
     <t>USD 96750.00 - 112500.00/year</t>
   </si>
   <si>
-    <t>Philanthropy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/431fc40128294bf883dbb9ca8e31364e-manager-of-finance-and-accounting-the-denver-foundation-denver</t>
   </si>
   <si>
+    <t>Manager of Service Corps Partnerships</t>
+  </si>
+  <si>
+    <t>FirstPic, Inc.</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/8ec08fb55bc04a878df321e0ed6f3aff-manager-of-service-corps-partnerships-firstpic-inc-annapolis</t>
+  </si>
+  <si>
     <t>Manager, Information Technology</t>
   </si>
   <si>
     <t>William T. Grant Foundation</t>
   </si>
   <si>
-    <t>USD 110000.00 - 120000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/30ae919c9aea446586bfb399bc335f2a-manager-information-technology-william-t-grant-foundation-new-york</t>
   </si>
   <si>
+    <t>Manager, Professional and Member Engagement</t>
+  </si>
+  <si>
+    <t>American Pharmacists Association</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0615871e1d7642a487b395781b757f94-manager-professional-and-member-engagement-american-pharmacists-association-washington</t>
+  </si>
+  <si>
     <t>Manager/Senior Manager of Policy</t>
   </si>
   <si>
@@ -1210,6 +1672,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/d5a2f9899ba6497fb5b54fc0205077ee-managing-director-baybrook-revitalization-fund-greater-baybrook-alliance-baltimore</t>
   </si>
   <si>
+    <t>Nourish Intake Associate (English/Spanish)</t>
+  </si>
+  <si>
+    <t>New York Common Pantry</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9806d2487ad34f069ff3de27442fa731-nourish-intake-associate-englishspanish-new-york-common-pantry-bronx</t>
+  </si>
+  <si>
+    <t>Office Manager at ICWC San Francisco Office</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ced37d3f6084449db3ac4fb8ac8197ba-office-manager-at-icwc-san-francisco-office-immigration-center-for-women-and-children-san-francisco</t>
+  </si>
+  <si>
     <t>Operations and Data Coordinator</t>
   </si>
   <si>
@@ -1234,21 +1726,54 @@
     <t>USD 65000.00 - 85000.00/year</t>
   </si>
   <si>
-    <t>Religion Spirituality</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/074964ae96e24887bc8ae27bc7214bcc-operations-manager-center-dc-washington</t>
   </si>
   <si>
+    <t>Outreach Coordinator (Disaster Legal Services) – Pro Bono Workgroup</t>
+  </si>
+  <si>
+    <t>USD 63265.00 - 71165.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c832ff3049e544fa90ac1c7f07487fed-outreach-coordinator-disaster-legal-services-pro-bono-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>OWA Member Support Specialist, Animal Welfare</t>
+  </si>
+  <si>
+    <t>The Humane League</t>
+  </si>
+  <si>
+    <t>USD 63166.00 - 77203.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb6fb48e99414dff888c37bf6310b421-owa-member-support-specialist-animal-welfare-the-humane-league-philadelphia</t>
+  </si>
+  <si>
+    <t>Program Coordinator II</t>
+  </si>
+  <si>
+    <t>Center for American Women and Politics (CAWP)</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6bf4d609aa0d4b37b47dcc4249e5feb4-program-coordinator-ii-center-for-american-women-and-politics-cawp-new-brunswick</t>
+  </si>
+  <si>
     <t>Program Director - Posse Los Angeles</t>
   </si>
   <si>
     <t>The Posse Foundation, Los Angeles</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -1267,6 +1792,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/340bc0c3ee554af094cfccbdd0305cc3-programmarketing-coordinator-center-dc-washington</t>
   </si>
   <si>
+    <t>Programme Officer - Community Health</t>
+  </si>
+  <si>
+    <t>SEED Madagascar</t>
+  </si>
+  <si>
+    <t>Taolagnaro, Anosy, MG</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94dab0f21f3b4bb385b28d5a4b780f5c-programme-officer-community-health-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Registered Nurse</t>
   </si>
   <si>
@@ -1282,6 +1822,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2d2fccb1657940a6b77485731a406468-registered-nurse-upper-manhattan-mental-health-center-inc-new-york</t>
   </si>
   <si>
+    <t>Rochester - Family Coach</t>
+  </si>
+  <si>
+    <t>Jeremiah Program_Minneapolis</t>
+  </si>
+  <si>
+    <t>Rochester, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Conflict Resolution, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aff719ed99d841bc8aa44d4c1206108c-rochester-family-coach-jeremiah-programminneapolis-rochester</t>
+  </si>
+  <si>
     <t>Senior Accountant</t>
   </si>
   <si>
@@ -1330,6 +1888,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/fa98f2fc29324e06aadf53f97261a4fb-senior-grants-manager-miami-waterkeeper-miami</t>
   </si>
   <si>
+    <t>Small Business Technical Assistance Provider (Co-op Organizer)</t>
+  </si>
+  <si>
+    <t>Boston Center for Community Ownership</t>
+  </si>
+  <si>
+    <t>USD 76500.00 - 76500.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08b1202044ec4af897fc25b29fd288ce-small-business-technical-assistance-provider-co-op-organizer-boston-center-for-community-ownership-boston</t>
+  </si>
+  <si>
+    <t>Social Media Manager &amp; Content Producer (Contract)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afdf3ea3c66b47d7b8850e4499053c72-social-media-manager-content-producer-contract-jewish-california-los-angeles</t>
+  </si>
+  <si>
     <t>Staff Attorney</t>
   </si>
   <si>
@@ -1357,6 +1942,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/42f210cefb1340eeb41bbf414a4c07bc-staff-attorney-legal-aid-society-of-eastern-virginia-norfolk</t>
   </si>
   <si>
+    <t>Student and Family Engagement Service Member</t>
+  </si>
+  <si>
+    <t>Kid Power, Inc.</t>
+  </si>
+  <si>
+    <t>USD 2000.00 - 2000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/498d9a224ce6475abf464c4afa7cb198-student-and-family-engagement-service-member-kid-power-inc-washington</t>
+  </si>
+  <si>
+    <t>Supervising Organizer Job Posting</t>
+  </si>
+  <si>
+    <t>Communities Resist</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f9e4d9a3046404280d2591b687b9de4-supervising-organizer-job-posting-communities-resist-brooklyn</t>
+  </si>
+  <si>
     <t>Team Lead Procurement HQ &amp; Internal Services</t>
   </si>
   <si>
@@ -1399,18 +2017,30 @@
     <t>Animal Care Centers of NYC</t>
   </si>
   <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
     <t>USD 26.44 - 26.44/hour</t>
   </si>
   <si>
-    <t>Animals</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/b53bda3599e1474bbf4cb765c97b9d8d-training-coordinator-animal-care-centers-of-nyc-new-york</t>
   </si>
   <si>
+    <t>TYSA Coalition Manager</t>
+  </si>
+  <si>
+    <t>Partnerships for Community Wellness</t>
+  </si>
+  <si>
+    <t>Richmond County, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48ef6cc0ff0b431aa5a95047f08d82e0-tysa-coalition-manager-partnerships-for-community-wellness-richmond-county</t>
+  </si>
+  <si>
     <t>Vice President of Programs</t>
   </si>
   <si>
@@ -1423,9 +2053,6 @@
     <t>USD 110000.00 - 115000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/fdd4d5b920e546578b65ff7e755dd7c3-vice-president-of-programs-prevent-child-abuse-new-jersey-north-brunswick-township</t>
   </si>
   <si>
@@ -1439,6 +2066,39 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4039a634179e444d8d135c56a9b4c11d-vice-president-strategy-and-planning-the-oakland-zoo-oakland</t>
+  </si>
+  <si>
+    <t>Volunteer &amp; Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Renewal Food Bank</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 26.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf8342120d864adda46f6ef5ba183087-volunteer-operations-coordinator-renewal-food-bank-bellevue</t>
+  </si>
+  <si>
+    <t>Youth Stabilization Specialist</t>
+  </si>
+  <si>
+    <t>exalt youth</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e30850c973145c2a3591863d55cfd60-youth-stabilization-specialist-exalt-youth-new-york</t>
   </si>
   <si>
     <t>ACADEMIC COORDINATOR I</t>
@@ -3400,7 +4060,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3496,200 +4156,200 @@
         <v>226</v>
       </c>
       <c r="D4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" t="s">
         <v>227</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>228</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" t="s">
         <v>231</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>232</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" t="s">
         <v>233</v>
       </c>
-      <c r="D5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>234</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F6" t="s">
+        <v>234</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" t="s">
-        <v>241</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
         <v>215</v>
       </c>
       <c r="E7" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="F7" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D8" t="s">
-        <v>215</v>
-      </c>
-      <c r="E8" t="s">
-        <v>251</v>
-      </c>
-      <c r="F8" t="s">
-        <v>252</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B9" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D9" t="s">
         <v>215</v>
       </c>
       <c r="E9" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F9" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="D10" t="s">
         <v>215</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B11" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D11" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="E11" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
         <v>215</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F12" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3697,919 +4357,2000 @@
         <v>271</v>
       </c>
       <c r="B13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F13" t="s">
+        <v>275</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="C13" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E13" t="s">
-        <v>262</v>
-      </c>
-      <c r="F13" t="s">
-        <v>278</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" t="s">
+        <v>279</v>
+      </c>
+      <c r="F14" t="s">
         <v>280</v>
       </c>
-      <c r="B14" t="s">
+      <c r="H14" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C14" t="s">
-        <v>282</v>
-      </c>
-      <c r="D14" t="s">
-        <v>215</v>
-      </c>
-      <c r="E14" t="s">
-        <v>283</v>
-      </c>
-      <c r="F14" t="s">
-        <v>263</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F15" t="s">
         <v>285</v>
       </c>
-      <c r="B15" t="s">
+      <c r="H15" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="C15" t="s">
-        <v>287</v>
-      </c>
-      <c r="D15" t="s">
-        <v>227</v>
-      </c>
-      <c r="E15" t="s">
-        <v>288</v>
-      </c>
-      <c r="F15" t="s">
-        <v>289</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D16" t="s">
+        <v>290</v>
+      </c>
+      <c r="E16" t="s">
         <v>291</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F16" t="s">
         <v>292</v>
       </c>
-      <c r="C16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D16" t="s">
-        <v>215</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="H16" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="F16" t="s">
-        <v>294</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" t="s">
         <v>296</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" t="s">
         <v>297</v>
       </c>
-      <c r="C17" t="s">
-        <v>245</v>
-      </c>
-      <c r="D17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>298</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B18" t="s">
         <v>301</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" t="s">
         <v>302</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>303</v>
       </c>
-      <c r="D18" t="s">
-        <v>215</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F18" t="s">
-        <v>305</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" t="s">
         <v>307</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" t="s">
         <v>308</v>
       </c>
-      <c r="C19" t="s">
-        <v>309</v>
-      </c>
-      <c r="D19" t="s">
-        <v>215</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>309</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="F19" t="s">
-        <v>311</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D20" t="s">
+        <v>215</v>
+      </c>
+      <c r="E20" t="s">
+        <v>312</v>
+      </c>
+      <c r="F20" t="s">
+        <v>234</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B20" t="s">
-        <v>314</v>
-      </c>
-      <c r="C20" t="s">
-        <v>245</v>
-      </c>
-      <c r="D20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E20" t="s">
-        <v>315</v>
-      </c>
-      <c r="F20" t="s">
-        <v>316</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>311</v>
       </c>
       <c r="B21" t="s">
-        <v>318</v>
+        <v>231</v>
       </c>
       <c r="C21" t="s">
-        <v>319</v>
+        <v>232</v>
       </c>
       <c r="D21" t="s">
         <v>215</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F21" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>315</v>
       </c>
       <c r="B22" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="C22" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D22" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="E22" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C23" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="D23" t="s">
         <v>215</v>
       </c>
       <c r="E23" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="F23" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B24" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C24" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D24" t="s">
         <v>215</v>
       </c>
       <c r="E24" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F24" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B25" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C25" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D25" t="s">
         <v>215</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="F25" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B26" t="s">
+        <v>337</v>
+      </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26" t="s">
+        <v>339</v>
+      </c>
+      <c r="F26" t="s">
+        <v>340</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="B26" t="s">
-        <v>342</v>
-      </c>
-      <c r="C26" t="s">
-        <v>245</v>
-      </c>
-      <c r="D26" t="s">
-        <v>215</v>
-      </c>
-      <c r="E26" t="s">
-        <v>343</v>
-      </c>
-      <c r="F26" t="s">
-        <v>344</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>342</v>
+      </c>
+      <c r="B27" t="s">
+        <v>343</v>
+      </c>
+      <c r="C27" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" t="s">
+        <v>215</v>
+      </c>
+      <c r="E27" t="s">
+        <v>344</v>
+      </c>
+      <c r="F27" t="s">
+        <v>345</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="B27" t="s">
-        <v>347</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>215</v>
-      </c>
-      <c r="E27" t="s">
-        <v>348</v>
-      </c>
-      <c r="F27" t="s">
-        <v>349</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>347</v>
+      </c>
+      <c r="B28" t="s">
+        <v>348</v>
+      </c>
+      <c r="C28" t="s">
+        <v>349</v>
+      </c>
+      <c r="D28" t="s">
+        <v>215</v>
+      </c>
+      <c r="E28" t="s">
+        <v>350</v>
+      </c>
+      <c r="F28" t="s">
         <v>351</v>
       </c>
-      <c r="B28" t="s">
-        <v>225</v>
-      </c>
-      <c r="C28" t="s">
-        <v>226</v>
-      </c>
-      <c r="D28" t="s">
-        <v>227</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="H28" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="F28" t="s">
-        <v>353</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B29" t="s">
+        <v>354</v>
+      </c>
+      <c r="C29" t="s">
+        <v>226</v>
+      </c>
+      <c r="D29" t="s">
+        <v>215</v>
+      </c>
+      <c r="E29" t="s">
         <v>355</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F29" t="s">
         <v>356</v>
       </c>
-      <c r="C29" t="s">
-        <v>303</v>
-      </c>
-      <c r="D29" t="s">
-        <v>215</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="H29" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="F29" t="s">
-        <v>358</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>358</v>
+      </c>
+      <c r="B30" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" t="s">
         <v>360</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" t="s">
         <v>361</v>
       </c>
-      <c r="C30" t="s">
+      <c r="F30" t="s">
+        <v>285</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E30" t="s">
-        <v>363</v>
-      </c>
-      <c r="F30" t="s">
-        <v>364</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" t="s">
+        <v>364</v>
+      </c>
+      <c r="D31" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F31" t="s">
+        <v>365</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="B31" t="s">
-        <v>367</v>
-      </c>
-      <c r="C31" t="s">
-        <v>368</v>
-      </c>
-      <c r="D31" t="s">
-        <v>369</v>
-      </c>
-      <c r="E31" t="s">
-        <v>370</v>
-      </c>
-      <c r="F31" t="s">
-        <v>335</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>367</v>
+      </c>
+      <c r="B32" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" t="s">
+        <v>369</v>
+      </c>
+      <c r="D32" t="s">
+        <v>261</v>
+      </c>
+      <c r="E32" t="s">
+        <v>370</v>
+      </c>
+      <c r="F32" t="s">
+        <v>371</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="B32" t="s">
-        <v>373</v>
-      </c>
-      <c r="C32" t="s">
-        <v>374</v>
-      </c>
-      <c r="D32" t="s">
-        <v>215</v>
-      </c>
-      <c r="E32" t="s">
-        <v>375</v>
-      </c>
-      <c r="F32" t="s">
-        <v>376</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B33" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
-        <v>380</v>
+        <v>207</v>
       </c>
       <c r="D33" t="s">
         <v>215</v>
       </c>
       <c r="E33" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="F33" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B34" t="s">
-        <v>385</v>
+        <v>225</v>
       </c>
       <c r="C34" t="s">
-        <v>245</v>
+        <v>369</v>
       </c>
       <c r="D34" t="s">
         <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F34" t="s">
-        <v>311</v>
+        <v>228</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B35" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C35" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D35" t="s">
         <v>215</v>
       </c>
       <c r="E35" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="F35" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B36" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C36" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="E36" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="F36" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B37" t="s">
-        <v>399</v>
+        <v>225</v>
       </c>
       <c r="C37" t="s">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="D37" t="s">
         <v>215</v>
       </c>
       <c r="E37" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="F37" t="s">
-        <v>288</v>
+        <v>228</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C38" t="s">
-        <v>303</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
         <v>215</v>
       </c>
       <c r="E38" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="F38" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C39" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D39" t="s">
         <v>215</v>
       </c>
       <c r="E39" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="F39" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C40" t="s">
-        <v>303</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
         <v>215</v>
       </c>
       <c r="E40" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F40" t="s">
-        <v>406</v>
+        <v>309</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
         <v>215</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F41" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C42" t="s">
-        <v>214</v>
+        <v>415</v>
       </c>
       <c r="D42" t="s">
         <v>215</v>
       </c>
       <c r="E42" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="F42" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="D43" t="s">
         <v>215</v>
       </c>
       <c r="E43" t="s">
-        <v>429</v>
+        <v>302</v>
       </c>
       <c r="F43" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C44" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D44" t="s">
         <v>215</v>
       </c>
       <c r="E44" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="F44" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C45" t="s">
-        <v>440</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E45" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="F45" t="s">
-        <v>263</v>
+        <v>432</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>438</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C46" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D46" t="s">
         <v>215</v>
       </c>
       <c r="E46" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="F46" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>447</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>286</v>
+        <v>438</v>
       </c>
       <c r="C47" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E47" t="s">
-        <v>288</v>
+        <v>440</v>
       </c>
       <c r="F47" t="s">
-        <v>289</v>
+        <v>441</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C48" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D48" t="s">
         <v>215</v>
       </c>
       <c r="E48" t="s">
-        <v>288</v>
+        <v>445</v>
       </c>
       <c r="F48" t="s">
-        <v>452</v>
+        <v>309</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>383</v>
       </c>
       <c r="D49" t="s">
-        <v>369</v>
+        <v>215</v>
       </c>
       <c r="E49" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="F49" t="s">
-        <v>457</v>
+        <v>309</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C50" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="D50" t="s">
         <v>215</v>
       </c>
       <c r="E50" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="F50" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B51" t="s">
-        <v>466</v>
+        <v>325</v>
       </c>
       <c r="C51" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D51" t="s">
         <v>215</v>
       </c>
       <c r="E51" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="F51" t="s">
-        <v>469</v>
+        <v>328</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>461</v>
+      </c>
+      <c r="B52" t="s">
+        <v>462</v>
+      </c>
+      <c r="C52" t="s">
+        <v>463</v>
+      </c>
+      <c r="D52" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" t="s">
+        <v>309</v>
+      </c>
+      <c r="F52" t="s">
+        <v>309</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>465</v>
+      </c>
+      <c r="B53" t="s">
+        <v>466</v>
+      </c>
+      <c r="C53" t="s">
+        <v>467</v>
+      </c>
+      <c r="D53" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" t="s">
+        <v>468</v>
+      </c>
+      <c r="F53" t="s">
+        <v>469</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>471</v>
       </c>
-      <c r="B52" t="s">
-        <v>238</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B54" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54" t="s">
+        <v>267</v>
+      </c>
+      <c r="D54" t="s">
+        <v>215</v>
+      </c>
+      <c r="E54" t="s">
         <v>472</v>
       </c>
-      <c r="D52" t="s">
-        <v>215</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F54" t="s">
+        <v>228</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="F52" t="s">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>474</v>
+      </c>
+      <c r="B55" t="s">
+        <v>475</v>
+      </c>
+      <c r="C55" t="s">
+        <v>476</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" t="s">
+        <v>477</v>
+      </c>
+      <c r="F55" t="s">
+        <v>478</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>480</v>
+      </c>
+      <c r="B56" t="s">
+        <v>481</v>
+      </c>
+      <c r="C56" t="s">
+        <v>267</v>
+      </c>
+      <c r="D56" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56" t="s">
+        <v>482</v>
+      </c>
+      <c r="F56" t="s">
+        <v>483</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>485</v>
+      </c>
+      <c r="B57" t="s">
+        <v>486</v>
+      </c>
+      <c r="C57" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E57" t="s">
+        <v>487</v>
+      </c>
+      <c r="F57" t="s">
+        <v>488</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>490</v>
+      </c>
+      <c r="B58" t="s">
+        <v>491</v>
+      </c>
+      <c r="C58" t="s">
+        <v>232</v>
+      </c>
+      <c r="D58" t="s">
+        <v>492</v>
+      </c>
+      <c r="E58" t="s">
+        <v>493</v>
+      </c>
+      <c r="F58" t="s">
+        <v>494</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>496</v>
+      </c>
+      <c r="B59" t="s">
+        <v>259</v>
+      </c>
+      <c r="C59" t="s">
+        <v>260</v>
+      </c>
+      <c r="D59" t="s">
+        <v>261</v>
+      </c>
+      <c r="E59" t="s">
+        <v>497</v>
+      </c>
+      <c r="F59" t="s">
+        <v>498</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>500</v>
+      </c>
+      <c r="B60" t="s">
+        <v>501</v>
+      </c>
+      <c r="C60" t="s">
+        <v>415</v>
+      </c>
+      <c r="D60" t="s">
+        <v>215</v>
+      </c>
+      <c r="E60" t="s">
+        <v>502</v>
+      </c>
+      <c r="F60" t="s">
+        <v>503</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>505</v>
+      </c>
+      <c r="B61" t="s">
+        <v>506</v>
+      </c>
+      <c r="C61" t="s">
+        <v>507</v>
+      </c>
+      <c r="D61" t="s">
+        <v>215</v>
+      </c>
+      <c r="E61" t="s">
+        <v>508</v>
+      </c>
+      <c r="F61" t="s">
+        <v>509</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>511</v>
+      </c>
+      <c r="B62" t="s">
+        <v>512</v>
+      </c>
+      <c r="C62" t="s">
+        <v>513</v>
+      </c>
+      <c r="D62" t="s">
+        <v>492</v>
+      </c>
+      <c r="E62" t="s">
+        <v>514</v>
+      </c>
+      <c r="F62" t="s">
+        <v>455</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>516</v>
+      </c>
+      <c r="B63" t="s">
+        <v>517</v>
+      </c>
+      <c r="C63" t="s">
+        <v>518</v>
+      </c>
+      <c r="D63" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" t="s">
+        <v>519</v>
+      </c>
+      <c r="F63" t="s">
+        <v>520</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>522</v>
+      </c>
+      <c r="B64" t="s">
+        <v>523</v>
+      </c>
+      <c r="C64" t="s">
+        <v>524</v>
+      </c>
+      <c r="D64" t="s">
+        <v>215</v>
+      </c>
+      <c r="E64" t="s">
+        <v>525</v>
+      </c>
+      <c r="F64" t="s">
+        <v>402</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>527</v>
+      </c>
+      <c r="B65" t="s">
+        <v>528</v>
+      </c>
+      <c r="C65" t="s">
+        <v>529</v>
+      </c>
+      <c r="D65" t="s">
+        <v>215</v>
+      </c>
+      <c r="E65" t="s">
+        <v>530</v>
+      </c>
+      <c r="F65" t="s">
+        <v>531</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>533</v>
+      </c>
+      <c r="B66" t="s">
+        <v>534</v>
+      </c>
+      <c r="C66" t="s">
+        <v>267</v>
+      </c>
+      <c r="D66" t="s">
+        <v>215</v>
+      </c>
+      <c r="E66" t="s">
+        <v>233</v>
+      </c>
+      <c r="F66" t="s">
+        <v>427</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>536</v>
+      </c>
+      <c r="B67" t="s">
+        <v>537</v>
+      </c>
+      <c r="C67" t="s">
+        <v>538</v>
+      </c>
+      <c r="D67" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" t="s">
+        <v>539</v>
+      </c>
+      <c r="F67" t="s">
+        <v>540</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>542</v>
+      </c>
+      <c r="B68" t="s">
+        <v>543</v>
+      </c>
+      <c r="C68" t="s">
+        <v>524</v>
+      </c>
+      <c r="D68" t="s">
+        <v>215</v>
+      </c>
+      <c r="E68" t="s">
+        <v>544</v>
+      </c>
+      <c r="F68" t="s">
+        <v>545</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>547</v>
+      </c>
+      <c r="B69" t="s">
+        <v>548</v>
+      </c>
+      <c r="C69" t="s">
+        <v>549</v>
+      </c>
+      <c r="D69" t="s">
+        <v>215</v>
+      </c>
+      <c r="E69" t="s">
+        <v>519</v>
+      </c>
+      <c r="F69" t="s">
+        <v>550</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>552</v>
+      </c>
+      <c r="B70" t="s">
+        <v>553</v>
+      </c>
+      <c r="C70" t="s">
+        <v>554</v>
+      </c>
+      <c r="D70" t="s">
+        <v>215</v>
+      </c>
+      <c r="E70" t="s">
+        <v>555</v>
+      </c>
+      <c r="F70" t="s">
+        <v>309</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>557</v>
+      </c>
+      <c r="B71" t="s">
+        <v>558</v>
+      </c>
+      <c r="C71" t="s">
+        <v>425</v>
+      </c>
+      <c r="D71" t="s">
+        <v>215</v>
+      </c>
+      <c r="E71" t="s">
+        <v>559</v>
+      </c>
+      <c r="F71" t="s">
+        <v>560</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>562</v>
+      </c>
+      <c r="B72" t="s">
+        <v>563</v>
+      </c>
+      <c r="C72" t="s">
+        <v>564</v>
+      </c>
+      <c r="D72" t="s">
+        <v>215</v>
+      </c>
+      <c r="E72" t="s">
+        <v>565</v>
+      </c>
+      <c r="F72" t="s">
+        <v>309</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>567</v>
+      </c>
+      <c r="B73" t="s">
+        <v>568</v>
+      </c>
+      <c r="C73" t="s">
+        <v>415</v>
+      </c>
+      <c r="D73" t="s">
+        <v>215</v>
+      </c>
+      <c r="E73" t="s">
+        <v>569</v>
+      </c>
+      <c r="F73" t="s">
+        <v>292</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>571</v>
+      </c>
+      <c r="B74" t="s">
         <v>241</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>474</v>
+      <c r="C74" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" t="s">
+        <v>215</v>
+      </c>
+      <c r="E74" t="s">
+        <v>572</v>
+      </c>
+      <c r="F74" t="s">
+        <v>244</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>574</v>
+      </c>
+      <c r="B75" t="s">
+        <v>575</v>
+      </c>
+      <c r="C75" t="s">
+        <v>207</v>
+      </c>
+      <c r="D75" t="s">
+        <v>215</v>
+      </c>
+      <c r="E75" t="s">
+        <v>576</v>
+      </c>
+      <c r="F75" t="s">
+        <v>577</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>579</v>
+      </c>
+      <c r="B76" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" t="s">
+        <v>581</v>
+      </c>
+      <c r="D76" t="s">
+        <v>215</v>
+      </c>
+      <c r="E76" t="s">
+        <v>309</v>
+      </c>
+      <c r="F76" t="s">
+        <v>582</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>584</v>
+      </c>
+      <c r="B77" t="s">
+        <v>585</v>
+      </c>
+      <c r="C77" t="s">
+        <v>236</v>
+      </c>
+      <c r="D77" t="s">
+        <v>215</v>
+      </c>
+      <c r="E77" t="s">
+        <v>586</v>
+      </c>
+      <c r="F77" t="s">
+        <v>587</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>589</v>
+      </c>
+      <c r="B78" t="s">
+        <v>568</v>
+      </c>
+      <c r="C78" t="s">
+        <v>415</v>
+      </c>
+      <c r="D78" t="s">
+        <v>215</v>
+      </c>
+      <c r="E78" t="s">
+        <v>590</v>
+      </c>
+      <c r="F78" t="s">
+        <v>292</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>592</v>
+      </c>
+      <c r="B79" t="s">
+        <v>593</v>
+      </c>
+      <c r="C79" t="s">
+        <v>594</v>
+      </c>
+      <c r="D79" t="s">
+        <v>215</v>
+      </c>
+      <c r="E79" t="s">
+        <v>309</v>
+      </c>
+      <c r="F79" t="s">
+        <v>595</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>597</v>
+      </c>
+      <c r="B80" t="s">
+        <v>598</v>
+      </c>
+      <c r="C80" t="s">
+        <v>267</v>
+      </c>
+      <c r="D80" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" t="s">
+        <v>599</v>
+      </c>
+      <c r="F80" t="s">
+        <v>600</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>602</v>
+      </c>
+      <c r="B81" t="s">
+        <v>603</v>
+      </c>
+      <c r="C81" t="s">
+        <v>604</v>
+      </c>
+      <c r="D81" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" t="s">
+        <v>605</v>
+      </c>
+      <c r="F81" t="s">
+        <v>606</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>608</v>
+      </c>
+      <c r="B82" t="s">
+        <v>609</v>
+      </c>
+      <c r="C82" t="s">
+        <v>214</v>
+      </c>
+      <c r="D82" t="s">
+        <v>215</v>
+      </c>
+      <c r="E82" t="s">
+        <v>610</v>
+      </c>
+      <c r="F82" t="s">
+        <v>611</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>613</v>
+      </c>
+      <c r="B83" t="s">
+        <v>614</v>
+      </c>
+      <c r="C83" t="s">
+        <v>207</v>
+      </c>
+      <c r="D83" t="s">
+        <v>215</v>
+      </c>
+      <c r="E83" t="s">
+        <v>615</v>
+      </c>
+      <c r="F83" t="s">
+        <v>616</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>618</v>
+      </c>
+      <c r="B84" t="s">
+        <v>619</v>
+      </c>
+      <c r="C84" t="s">
+        <v>620</v>
+      </c>
+      <c r="D84" t="s">
+        <v>215</v>
+      </c>
+      <c r="E84" t="s">
+        <v>621</v>
+      </c>
+      <c r="F84" t="s">
+        <v>622</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>624</v>
+      </c>
+      <c r="B85" t="s">
+        <v>625</v>
+      </c>
+      <c r="C85" t="s">
+        <v>289</v>
+      </c>
+      <c r="D85" t="s">
+        <v>215</v>
+      </c>
+      <c r="E85" t="s">
+        <v>626</v>
+      </c>
+      <c r="F85" t="s">
+        <v>627</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>629</v>
+      </c>
+      <c r="B86" t="s">
+        <v>368</v>
+      </c>
+      <c r="C86" t="s">
+        <v>207</v>
+      </c>
+      <c r="D86" t="s">
+        <v>630</v>
+      </c>
+      <c r="E86" t="s">
+        <v>631</v>
+      </c>
+      <c r="F86" t="s">
+        <v>371</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>633</v>
+      </c>
+      <c r="B87" t="s">
+        <v>634</v>
+      </c>
+      <c r="C87" t="s">
+        <v>635</v>
+      </c>
+      <c r="D87" t="s">
+        <v>261</v>
+      </c>
+      <c r="E87" t="s">
+        <v>636</v>
+      </c>
+      <c r="F87" t="s">
+        <v>345</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>633</v>
+      </c>
+      <c r="B88" t="s">
+        <v>638</v>
+      </c>
+      <c r="C88" t="s">
+        <v>639</v>
+      </c>
+      <c r="D88" t="s">
+        <v>215</v>
+      </c>
+      <c r="E88" t="s">
+        <v>640</v>
+      </c>
+      <c r="F88" t="s">
+        <v>309</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>642</v>
+      </c>
+      <c r="B89" t="s">
+        <v>643</v>
+      </c>
+      <c r="C89" t="s">
+        <v>415</v>
+      </c>
+      <c r="D89" t="s">
+        <v>215</v>
+      </c>
+      <c r="E89" t="s">
+        <v>644</v>
+      </c>
+      <c r="F89" t="s">
+        <v>645</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>647</v>
+      </c>
+      <c r="B90" t="s">
+        <v>648</v>
+      </c>
+      <c r="C90" t="s">
+        <v>649</v>
+      </c>
+      <c r="D90" t="s">
+        <v>215</v>
+      </c>
+      <c r="E90" t="s">
+        <v>650</v>
+      </c>
+      <c r="F90" t="s">
+        <v>651</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>653</v>
+      </c>
+      <c r="B91" t="s">
+        <v>387</v>
+      </c>
+      <c r="C91" t="s">
+        <v>654</v>
+      </c>
+      <c r="D91" t="s">
+        <v>261</v>
+      </c>
+      <c r="E91" t="s">
+        <v>309</v>
+      </c>
+      <c r="F91" t="s">
+        <v>389</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>656</v>
+      </c>
+      <c r="B92" t="s">
+        <v>657</v>
+      </c>
+      <c r="C92" t="s">
+        <v>207</v>
+      </c>
+      <c r="D92" t="s">
+        <v>215</v>
+      </c>
+      <c r="E92" t="s">
+        <v>309</v>
+      </c>
+      <c r="F92" t="s">
+        <v>658</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>660</v>
+      </c>
+      <c r="B93" t="s">
+        <v>661</v>
+      </c>
+      <c r="C93" t="s">
+        <v>267</v>
+      </c>
+      <c r="D93" t="s">
+        <v>492</v>
+      </c>
+      <c r="E93" t="s">
+        <v>662</v>
+      </c>
+      <c r="F93" t="s">
+        <v>663</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>665</v>
+      </c>
+      <c r="B94" t="s">
+        <v>666</v>
+      </c>
+      <c r="C94" t="s">
+        <v>226</v>
+      </c>
+      <c r="D94" t="s">
+        <v>215</v>
+      </c>
+      <c r="E94" t="s">
+        <v>667</v>
+      </c>
+      <c r="F94" t="s">
+        <v>577</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>669</v>
+      </c>
+      <c r="B95" t="s">
+        <v>670</v>
+      </c>
+      <c r="C95" t="s">
+        <v>671</v>
+      </c>
+      <c r="D95" t="s">
+        <v>215</v>
+      </c>
+      <c r="E95" t="s">
+        <v>672</v>
+      </c>
+      <c r="F95" t="s">
+        <v>673</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>675</v>
+      </c>
+      <c r="B96" t="s">
+        <v>676</v>
+      </c>
+      <c r="C96" t="s">
+        <v>677</v>
+      </c>
+      <c r="D96" t="s">
+        <v>215</v>
+      </c>
+      <c r="E96" t="s">
+        <v>678</v>
+      </c>
+      <c r="F96" t="s">
+        <v>531</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>680</v>
+      </c>
+      <c r="B97" t="s">
+        <v>278</v>
+      </c>
+      <c r="C97" t="s">
+        <v>681</v>
+      </c>
+      <c r="D97" t="s">
+        <v>215</v>
+      </c>
+      <c r="E97" t="s">
+        <v>682</v>
+      </c>
+      <c r="F97" t="s">
+        <v>280</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>684</v>
+      </c>
+      <c r="B98" t="s">
+        <v>685</v>
+      </c>
+      <c r="C98" t="s">
+        <v>686</v>
+      </c>
+      <c r="D98" t="s">
+        <v>215</v>
+      </c>
+      <c r="E98" t="s">
+        <v>687</v>
+      </c>
+      <c r="F98" t="s">
+        <v>688</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>690</v>
+      </c>
+      <c r="B99" t="s">
+        <v>691</v>
+      </c>
+      <c r="C99" t="s">
+        <v>267</v>
+      </c>
+      <c r="D99" t="s">
+        <v>215</v>
+      </c>
+      <c r="E99" t="s">
+        <v>692</v>
+      </c>
+      <c r="F99" t="s">
+        <v>693</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -4666,6 +6407,53 @@
     <hyperlink ref="H50" r:id="rId49"/>
     <hyperlink ref="H51" r:id="rId50"/>
     <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4715,1109 +6503,1109 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>475</v>
+        <v>695</v>
       </c>
       <c r="B2" t="s">
-        <v>476</v>
+        <v>696</v>
       </c>
       <c r="C2" t="s">
-        <v>477</v>
+        <v>697</v>
       </c>
       <c r="D2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F2" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>479</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="B3" t="s">
-        <v>481</v>
+        <v>701</v>
       </c>
       <c r="C3" t="s">
-        <v>482</v>
+        <v>702</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E3" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F3" t="s">
-        <v>483</v>
+        <v>703</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>484</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>705</v>
       </c>
       <c r="B4" t="s">
-        <v>486</v>
+        <v>706</v>
       </c>
       <c r="C4" t="s">
-        <v>487</v>
+        <v>707</v>
       </c>
       <c r="D4" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F4" t="s">
-        <v>483</v>
+        <v>703</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>488</v>
+        <v>708</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>489</v>
+        <v>709</v>
       </c>
       <c r="B5" t="s">
-        <v>490</v>
+        <v>710</v>
       </c>
       <c r="C5" t="s">
-        <v>491</v>
+        <v>711</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F5" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>492</v>
+        <v>712</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>493</v>
+        <v>713</v>
       </c>
       <c r="B6" t="s">
-        <v>494</v>
+        <v>714</v>
       </c>
       <c r="C6" t="s">
-        <v>495</v>
+        <v>715</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E6" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F6" t="s">
-        <v>335</v>
+        <v>455</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>496</v>
+        <v>716</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>717</v>
       </c>
       <c r="B7" t="s">
-        <v>498</v>
+        <v>718</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E7" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F7" t="s">
-        <v>483</v>
+        <v>703</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>499</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>500</v>
+        <v>720</v>
       </c>
       <c r="B8" t="s">
-        <v>501</v>
+        <v>721</v>
       </c>
       <c r="C8" t="s">
-        <v>502</v>
+        <v>722</v>
       </c>
       <c r="D8" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E8" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F8" t="s">
-        <v>503</v>
+        <v>723</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>504</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>505</v>
+        <v>725</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>506</v>
+        <v>726</v>
       </c>
       <c r="D9" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F9" t="s">
-        <v>507</v>
+        <v>727</v>
       </c>
       <c r="G9" t="s">
-        <v>508</v>
+        <v>728</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>509</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>510</v>
+        <v>730</v>
       </c>
       <c r="B10" t="s">
-        <v>481</v>
+        <v>701</v>
       </c>
       <c r="C10" t="s">
-        <v>482</v>
+        <v>702</v>
       </c>
       <c r="D10" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E10" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F10" t="s">
-        <v>511</v>
+        <v>731</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>512</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>513</v>
+        <v>733</v>
       </c>
       <c r="B11" t="s">
-        <v>514</v>
+        <v>734</v>
       </c>
       <c r="C11" t="s">
-        <v>515</v>
+        <v>735</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E11" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F11" t="s">
-        <v>516</v>
+        <v>736</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>517</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>518</v>
+        <v>738</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>739</v>
       </c>
       <c r="C12" t="s">
-        <v>520</v>
+        <v>740</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E12" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F12" t="s">
-        <v>516</v>
+        <v>736</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>521</v>
+        <v>741</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>522</v>
+        <v>742</v>
       </c>
       <c r="B13" t="s">
-        <v>523</v>
+        <v>743</v>
       </c>
       <c r="C13" t="s">
         <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E13" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F13" t="s">
-        <v>511</v>
+        <v>731</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>524</v>
+        <v>744</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>525</v>
+        <v>745</v>
       </c>
       <c r="B14" t="s">
-        <v>526</v>
+        <v>746</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>747</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E14" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F14" t="s">
-        <v>528</v>
+        <v>748</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>529</v>
+        <v>749</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>530</v>
+        <v>750</v>
       </c>
       <c r="B15" t="s">
-        <v>531</v>
+        <v>751</v>
       </c>
       <c r="C15" t="s">
-        <v>532</v>
+        <v>752</v>
       </c>
       <c r="D15" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E15" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F15" t="s">
-        <v>511</v>
+        <v>731</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>533</v>
+        <v>753</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>534</v>
+        <v>754</v>
       </c>
       <c r="C16" t="s">
-        <v>535</v>
+        <v>755</v>
       </c>
       <c r="D16" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E16" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F16" t="s">
-        <v>511</v>
+        <v>731</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>536</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>537</v>
+        <v>757</v>
       </c>
       <c r="B17" t="s">
-        <v>538</v>
+        <v>758</v>
       </c>
       <c r="C17" t="s">
-        <v>539</v>
+        <v>759</v>
       </c>
       <c r="D17" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E17" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F17" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>540</v>
+        <v>760</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>541</v>
+        <v>761</v>
       </c>
       <c r="B18" t="s">
-        <v>542</v>
+        <v>762</v>
       </c>
       <c r="C18" t="s">
-        <v>543</v>
+        <v>763</v>
       </c>
       <c r="D18" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E18" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F18" t="s">
         <v>103</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>544</v>
+        <v>764</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>545</v>
+        <v>765</v>
       </c>
       <c r="B19" t="s">
-        <v>546</v>
+        <v>766</v>
       </c>
       <c r="C19" t="s">
-        <v>547</v>
+        <v>767</v>
       </c>
       <c r="D19" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E19" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F19" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>548</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>549</v>
+        <v>769</v>
       </c>
       <c r="B20" t="s">
-        <v>550</v>
+        <v>770</v>
       </c>
       <c r="C20" t="s">
-        <v>551</v>
+        <v>771</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E20" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F20" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>552</v>
+        <v>772</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>553</v>
+        <v>773</v>
       </c>
       <c r="B21" t="s">
-        <v>554</v>
+        <v>774</v>
       </c>
       <c r="C21" t="s">
-        <v>543</v>
+        <v>763</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E21" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F21" t="s">
-        <v>483</v>
+        <v>703</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>555</v>
+        <v>775</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>556</v>
+        <v>776</v>
       </c>
       <c r="B22" t="s">
-        <v>557</v>
+        <v>777</v>
       </c>
       <c r="C22" t="s">
-        <v>558</v>
+        <v>778</v>
       </c>
       <c r="D22" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E22" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F22" t="s">
-        <v>528</v>
+        <v>748</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>559</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>560</v>
+        <v>780</v>
       </c>
       <c r="B23" t="s">
-        <v>561</v>
+        <v>781</v>
       </c>
       <c r="C23" t="s">
-        <v>562</v>
+        <v>782</v>
       </c>
       <c r="D23" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E23" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F23" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>563</v>
+        <v>783</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>564</v>
+        <v>784</v>
       </c>
       <c r="B24" t="s">
-        <v>565</v>
+        <v>785</v>
       </c>
       <c r="C24" t="s">
-        <v>566</v>
+        <v>786</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E24" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F24" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>567</v>
+        <v>787</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>568</v>
+        <v>788</v>
       </c>
       <c r="B25" t="s">
-        <v>569</v>
+        <v>789</v>
       </c>
       <c r="C25" t="s">
-        <v>570</v>
+        <v>790</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F25" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>571</v>
+        <v>791</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>572</v>
+        <v>792</v>
       </c>
       <c r="B26" t="s">
-        <v>573</v>
+        <v>793</v>
       </c>
       <c r="C26" t="s">
-        <v>574</v>
+        <v>794</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E26" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F26" t="s">
-        <v>503</v>
+        <v>723</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>575</v>
+        <v>795</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>576</v>
+        <v>796</v>
       </c>
       <c r="B27" t="s">
-        <v>577</v>
+        <v>797</v>
       </c>
       <c r="C27" t="s">
-        <v>578</v>
+        <v>798</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E27" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F27" t="s">
-        <v>503</v>
+        <v>723</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>579</v>
+        <v>799</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>580</v>
+        <v>800</v>
       </c>
       <c r="B28" t="s">
-        <v>581</v>
+        <v>801</v>
       </c>
       <c r="C28" t="s">
-        <v>487</v>
+        <v>707</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E28" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F28" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>582</v>
+        <v>802</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>583</v>
+        <v>803</v>
       </c>
       <c r="B29" t="s">
-        <v>584</v>
+        <v>804</v>
       </c>
       <c r="C29" t="s">
-        <v>520</v>
+        <v>740</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E29" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F29" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>585</v>
+        <v>805</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>586</v>
+        <v>806</v>
       </c>
       <c r="B30" t="s">
-        <v>587</v>
+        <v>807</v>
       </c>
       <c r="C30" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E30" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F30" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>588</v>
+        <v>808</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>589</v>
+        <v>809</v>
       </c>
       <c r="B31" t="s">
-        <v>590</v>
+        <v>810</v>
       </c>
       <c r="C31" t="s">
-        <v>591</v>
+        <v>811</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E31" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F31" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>592</v>
+        <v>812</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>593</v>
+        <v>813</v>
       </c>
       <c r="B32" t="s">
-        <v>594</v>
+        <v>814</v>
       </c>
       <c r="C32" t="s">
-        <v>380</v>
+        <v>524</v>
       </c>
       <c r="D32" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E32" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F32" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>595</v>
+        <v>815</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>596</v>
+        <v>816</v>
       </c>
       <c r="B33" t="s">
-        <v>597</v>
+        <v>817</v>
       </c>
       <c r="C33" t="s">
-        <v>598</v>
+        <v>818</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E33" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F33" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>599</v>
+        <v>819</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>600</v>
+        <v>820</v>
       </c>
       <c r="B34" t="s">
-        <v>601</v>
+        <v>821</v>
       </c>
       <c r="C34" t="s">
-        <v>602</v>
+        <v>822</v>
       </c>
       <c r="D34" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E34" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F34" t="s">
-        <v>528</v>
+        <v>748</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>603</v>
+        <v>823</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>604</v>
+        <v>824</v>
       </c>
       <c r="B35" t="s">
-        <v>605</v>
+        <v>825</v>
       </c>
       <c r="C35" t="s">
-        <v>606</v>
+        <v>826</v>
       </c>
       <c r="D35" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F35" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>607</v>
+        <v>827</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>608</v>
+        <v>828</v>
       </c>
       <c r="B36" t="s">
-        <v>609</v>
+        <v>829</v>
       </c>
       <c r="C36" t="s">
-        <v>610</v>
+        <v>830</v>
       </c>
       <c r="D36" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E36" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F36" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>611</v>
+        <v>831</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>608</v>
+        <v>828</v>
       </c>
       <c r="B37" t="s">
-        <v>612</v>
+        <v>832</v>
       </c>
       <c r="C37" t="s">
         <v>66</v>
       </c>
       <c r="D37" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E37" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F37" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>613</v>
+        <v>833</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>614</v>
+        <v>834</v>
       </c>
       <c r="B38" t="s">
-        <v>615</v>
+        <v>835</v>
       </c>
       <c r="C38" t="s">
-        <v>616</v>
+        <v>836</v>
       </c>
       <c r="D38" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E38" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F38" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>617</v>
+        <v>837</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>618</v>
+        <v>838</v>
       </c>
       <c r="B39" t="s">
-        <v>619</v>
+        <v>839</v>
       </c>
       <c r="C39" t="s">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="D39" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E39" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F39" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>621</v>
+        <v>841</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>622</v>
+        <v>842</v>
       </c>
       <c r="B40" t="s">
-        <v>526</v>
+        <v>746</v>
       </c>
       <c r="C40" t="s">
-        <v>527</v>
+        <v>747</v>
       </c>
       <c r="D40" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E40" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F40" t="s">
-        <v>528</v>
+        <v>748</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>623</v>
+        <v>843</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>624</v>
+        <v>844</v>
       </c>
       <c r="B41" t="s">
-        <v>625</v>
+        <v>845</v>
       </c>
       <c r="C41" t="s">
-        <v>626</v>
+        <v>846</v>
       </c>
       <c r="D41" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E41" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F41" t="s">
-        <v>627</v>
+        <v>847</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>628</v>
+        <v>848</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>629</v>
+        <v>849</v>
       </c>
       <c r="B42" t="s">
-        <v>590</v>
+        <v>810</v>
       </c>
       <c r="C42" t="s">
-        <v>630</v>
+        <v>850</v>
       </c>
       <c r="D42" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E42" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F42" t="s">
-        <v>627</v>
+        <v>847</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>631</v>
+        <v>851</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>632</v>
+        <v>852</v>
       </c>
       <c r="B43" t="s">
-        <v>490</v>
+        <v>710</v>
       </c>
       <c r="C43" t="s">
-        <v>491</v>
+        <v>711</v>
       </c>
       <c r="D43" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E43" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F43" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>633</v>
+        <v>853</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>634</v>
+        <v>854</v>
       </c>
       <c r="B44" t="s">
-        <v>635</v>
+        <v>855</v>
       </c>
       <c r="C44" t="s">
-        <v>636</v>
+        <v>856</v>
       </c>
       <c r="D44" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E44" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F44" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>637</v>
+        <v>857</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>638</v>
+        <v>858</v>
       </c>
       <c r="B45" t="s">
-        <v>639</v>
+        <v>859</v>
       </c>
       <c r="C45" t="s">
         <v>66</v>
       </c>
       <c r="D45" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E45" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F45" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>641</v>
+        <v>861</v>
       </c>
       <c r="B46" t="s">
-        <v>639</v>
+        <v>859</v>
       </c>
       <c r="C46" t="s">
         <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E46" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F46" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>642</v>
+        <v>862</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>643</v>
+        <v>863</v>
       </c>
       <c r="B47" t="s">
-        <v>644</v>
+        <v>864</v>
       </c>
       <c r="C47" t="s">
-        <v>645</v>
+        <v>865</v>
       </c>
       <c r="D47" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E47" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F47" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>646</v>
+        <v>866</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>647</v>
+        <v>867</v>
       </c>
       <c r="B48" t="s">
-        <v>590</v>
+        <v>810</v>
       </c>
       <c r="C48" t="s">
-        <v>648</v>
+        <v>868</v>
       </c>
       <c r="D48" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E48" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F48" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>649</v>
+        <v>869</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>870</v>
       </c>
       <c r="B49" t="s">
-        <v>651</v>
+        <v>871</v>
       </c>
       <c r="C49" t="s">
-        <v>652</v>
+        <v>872</v>
       </c>
       <c r="D49" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E49" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F49" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>653</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
